--- a/Hemnet modell.xlsx
+++ b/Hemnet modell.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C412FC7-D4BA-EB42-B344-FDBBDD58D4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E8E4F0-15E2-4E47-B649-6B19E2111F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25240" yWindow="500" windowWidth="25960" windowHeight="26740" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Modell" sheetId="2" r:id="rId2"/>
-    <sheet name="Nøkkeltall" sheetId="3" r:id="rId3"/>
-    <sheet name="Nedsideberegning" sheetId="5" r:id="rId4"/>
+    <sheet name="Månedstall" sheetId="6" r:id="rId3"/>
+    <sheet name="Nøkkeltall" sheetId="3" r:id="rId4"/>
+    <sheet name="Nedsideberegning" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="176">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -281,9 +282,6 @@
     <t>Right of use assets</t>
   </si>
   <si>
-    <t>Other non-curretn assets</t>
-  </si>
-  <si>
     <t>accounts receivables</t>
   </si>
   <si>
@@ -420,6 +418,183 @@
   </si>
   <si>
     <t>0% vekst og konstante marginer</t>
+  </si>
+  <si>
+    <t>Press releases:</t>
+  </si>
+  <si>
+    <t>Tilbakekjøpsprogram</t>
+  </si>
+  <si>
+    <t>Dato kjøp</t>
+  </si>
+  <si>
+    <t>Antall aksjer</t>
+  </si>
+  <si>
+    <t>Akummelert antall aksjer</t>
+  </si>
+  <si>
+    <t>Kjøp </t>
+  </si>
+  <si>
+    <t>Akkumelert kjøp </t>
+  </si>
+  <si>
+    <t>Other non-current assets</t>
+  </si>
+  <si>
+    <t>08.05.26: Hemnet starter nytt tilbakekjøpsprogram på opptil 600 SEKm</t>
+  </si>
+  <si>
+    <t>Januar</t>
+  </si>
+  <si>
+    <t>Februar</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>april</t>
+  </si>
+  <si>
+    <t>mai</t>
+  </si>
+  <si>
+    <t>juni</t>
+  </si>
+  <si>
+    <t>Net sales, total</t>
+  </si>
+  <si>
+    <t>Net sales, property sellers</t>
+  </si>
+  <si>
+    <t>Net sales B2B</t>
+  </si>
+  <si>
+    <t>ARPL paid</t>
+  </si>
+  <si>
+    <t>Published listings (thousand)</t>
+  </si>
+  <si>
+    <t>Paid listings (thousand)</t>
+  </si>
+  <si>
+    <t>juli</t>
+  </si>
+  <si>
+    <t>august</t>
+  </si>
+  <si>
+    <t>september</t>
+  </si>
+  <si>
+    <t>oktober</t>
+  </si>
+  <si>
+    <t>november</t>
+  </si>
+  <si>
+    <t>desember</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>18.05.26: Hemnet kjøper tilbake 80 000 aksjer</t>
+  </si>
+  <si>
+    <t>25.05.26: Hemnet kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>01.06.26: Hemnet kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>08.06.26: Hemnet kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>15.06.26: Hemnet kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>22.06.26: CFO Anders Örnulf har bestemt seg for å forlate Hemnet. Ny CFO Peter Messner vil starte 20.juli 2026</t>
+  </si>
+  <si>
+    <t>22.06.26: Hemnet kjøper tilbake 120 000 aksjer</t>
+  </si>
+  <si>
+    <t>07.05.26: Hemnet kjøper tilbake 92 000 aksjer og fullfører tilbakekjøpsprogrammet sitt</t>
+  </si>
+  <si>
+    <t>04.05.26: Hemnet kjøper tilbake 175 000 aksjer</t>
+  </si>
+  <si>
+    <t>27.04.26: Hemnet kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>20.04.26: Hemnet kjøper tilbake 100 000 aksjer</t>
+  </si>
+  <si>
+    <t>13.04.26: Hemnet kjøper tilbake 80 000 aksjer</t>
+  </si>
+  <si>
+    <t>07.04.26: Hemnet kjøper tilbake 80 000 aksjer</t>
+  </si>
+  <si>
+    <t>30.03.26: Hemnet kjøper tilbake 143 050 aksjer</t>
+  </si>
+  <si>
+    <t>29.06.26: Hemnet kjøper tilbake 150 000 aksjer</t>
+  </si>
+  <si>
+    <t>Gearing</t>
+  </si>
+  <si>
+    <t>06.07.26: Hemnet kjøper tilbake 150 000 aksjer</t>
+  </si>
+  <si>
+    <t>13.07.26: Hemnet kjøper tilbake 150 000 aksjer</t>
+  </si>
+  <si>
+    <t>20.07.26: Hemnet kjøper tilbake 139 314 aksjer</t>
+  </si>
+  <si>
+    <t>27.07.26: Hemnet kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>03.08.26: hemnet kjøper tilbake 123 000 aksjer</t>
+  </si>
+  <si>
+    <t>10.08.26: Hemnet kjøper tilbake 120 000 aksjer</t>
+  </si>
+  <si>
+    <t>17.08.26: Hemnet kjøper tilbake 120 000 aksjer</t>
+  </si>
+  <si>
+    <t>24.08.26: Hemnet kjøper tilbake 233 610 aksjer</t>
+  </si>
+  <si>
+    <t>31.08.26: Hemnet kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>07.09.26: Hemnet kjøper tilbake  125 000 aksjer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09.07.26: Hemnet setter tilbakekjøpsprogrammet på pause </t>
+  </si>
+  <si>
+    <t>Setter programmet på pause</t>
   </si>
 </sst>
 </file>
@@ -432,7 +607,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0\ %"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -493,13 +668,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -547,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -590,7 +800,33 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,55 +842,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>707815</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Bilde 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC70D8B5-F617-D38D-714F-9390E9F92586}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9194800" y="25400"/>
-          <a:ext cx="4505115" cy="10058400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -969,35 +1156,816 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{F5297D19-5566-404E-9DBE-2FC34F16CAA5}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;73499f08-ec3b-4b64-8dba-6685d7273fc4&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
-  <dimension ref="A5:G19"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="10.83203125" style="2"/>
     <col min="7" max="7" width="18.83203125" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="2"/>
+    <col min="8" max="11" width="10.83203125" style="2"/>
+    <col min="12" max="12" width="25.5" style="43" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" style="44" customWidth="1"/>
+    <col min="14" max="14" width="26.1640625" style="44" customWidth="1"/>
+    <col min="15" max="15" width="13" style="44" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" style="44" customWidth="1"/>
+    <col min="17" max="18" width="10.83203125" style="2"/>
+    <col min="19" max="19" width="23.1640625" style="42" customWidth="1"/>
+    <col min="20" max="20" width="17.83203125" style="44" customWidth="1"/>
+    <col min="21" max="21" width="28.6640625" style="44" customWidth="1"/>
+    <col min="22" max="22" width="13.1640625" style="44" customWidth="1"/>
+    <col min="23" max="23" width="15.6640625" style="44" customWidth="1"/>
+    <col min="24" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9"/>
+      <c r="S9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L11" s="42">
+        <v>46160</v>
+      </c>
+      <c r="M11" s="44">
+        <v>80000</v>
+      </c>
+      <c r="N11" s="44">
+        <f>M11</f>
+        <v>80000</v>
+      </c>
+      <c r="O11" s="44">
+        <f>2060336+2150884+2151590+2201280</f>
+        <v>8564090</v>
+      </c>
+      <c r="P11" s="44">
+        <f>O11</f>
+        <v>8564090</v>
+      </c>
+      <c r="S11" s="42">
+        <v>46111</v>
+      </c>
+      <c r="T11" s="44">
+        <v>143050</v>
+      </c>
+      <c r="U11" s="44">
+        <f>T11</f>
+        <v>143050</v>
+      </c>
+      <c r="V11" s="44">
+        <f>2098438+2056670+2089808+6496357+2009566</f>
+        <v>14750839</v>
+      </c>
+      <c r="W11" s="44">
+        <f>V11</f>
+        <v>14750839</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L12" s="42">
+        <v>46167</v>
+      </c>
+      <c r="M12" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N12" s="44">
+        <f>SUM(M11:M12)</f>
+        <v>205000</v>
+      </c>
+      <c r="O12" s="44">
+        <f>2367668+2414588+2333464+2452363+2434958</f>
+        <v>12003041</v>
+      </c>
+      <c r="P12" s="44">
+        <f>SUM(O11:O12)</f>
+        <v>20567131</v>
+      </c>
+      <c r="S12" s="42">
+        <v>46119</v>
+      </c>
+      <c r="T12" s="44">
+        <v>80000</v>
+      </c>
+      <c r="U12" s="44">
+        <f>SUM(T11:T12)</f>
+        <v>223050</v>
+      </c>
+      <c r="V12" s="44">
+        <f>1981314+2098874+2135638+2113074</f>
+        <v>8328900</v>
+      </c>
+      <c r="W12" s="44">
+        <f>SUM(V11:V12)</f>
+        <v>23079739</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L13" s="42">
+        <v>46174</v>
+      </c>
+      <c r="M13" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N13" s="44">
+        <f>SUM(M11:M13)</f>
+        <v>330000</v>
+      </c>
+      <c r="O13" s="44">
+        <f>2357160+2295290+2400070+2435685+2523293</f>
+        <v>12011498</v>
+      </c>
+      <c r="P13" s="44">
+        <f>SUM(O11:O13)</f>
+        <v>32578629</v>
+      </c>
+      <c r="S13" s="42">
+        <v>46125</v>
+      </c>
+      <c r="T13" s="44">
+        <v>80000</v>
+      </c>
+      <c r="U13" s="44">
+        <f>SUM(T11:T13)</f>
+        <v>303050</v>
+      </c>
+      <c r="V13" s="44">
+        <f>2188888+2292750+2147558+2169802</f>
+        <v>8798998</v>
+      </c>
+      <c r="W13" s="44">
+        <f>SUM(V11:V13)</f>
+        <v>31878737</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L14" s="42">
+        <v>46181</v>
+      </c>
+      <c r="M14" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N14" s="44">
+        <f>SUM(M11:M14)</f>
+        <v>455000</v>
+      </c>
+      <c r="O14" s="44">
+        <f>2317923+2265573+2277198+2427205+2423010</f>
+        <v>11710909</v>
+      </c>
+      <c r="P14" s="44">
+        <f>SUM(O11:O14)</f>
+        <v>44289538</v>
+      </c>
+      <c r="S14" s="42">
+        <v>46132</v>
+      </c>
+      <c r="T14" s="44">
+        <v>100000</v>
+      </c>
+      <c r="U14" s="44">
+        <f>SUM(T11:T14)</f>
+        <v>403050</v>
+      </c>
+      <c r="V14" s="44">
+        <f>2121074+2210124+2232266+2363304+2476244</f>
+        <v>11403012</v>
+      </c>
+      <c r="W14" s="44">
+        <f>SUM(V11:V14)</f>
+        <v>43281749</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L15" s="42">
+        <v>46188</v>
+      </c>
+      <c r="M15" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N15" s="44">
+        <f>SUM(M11:M15)</f>
+        <v>580000</v>
+      </c>
+      <c r="O15" s="44">
+        <f>2053298+2134355+2142228+2204675+2281223</f>
+        <v>10815779</v>
+      </c>
+      <c r="P15" s="44">
+        <f>SUM(O11:O15)</f>
+        <v>55105317</v>
+      </c>
+      <c r="S15" s="42">
+        <v>46139</v>
+      </c>
+      <c r="T15" s="44">
+        <v>100000</v>
+      </c>
+      <c r="U15" s="44">
+        <f>SUM(T11:T15)</f>
+        <v>503050</v>
+      </c>
+      <c r="V15" s="44">
+        <f>2439114+2459594+2409192+2384776+2282340</f>
+        <v>11975016</v>
+      </c>
+      <c r="W15" s="44">
+        <f>SUM(V11:V15)</f>
+        <v>55256765</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L16" s="42">
+        <v>46195</v>
+      </c>
+      <c r="M16" s="44">
+        <v>120000</v>
+      </c>
+      <c r="N16" s="44">
+        <f>SUM(M11:M16)</f>
+        <v>700000</v>
+      </c>
+      <c r="O16" s="44">
+        <f>2163444+2189877+2208306+2302131</f>
+        <v>8863758</v>
+      </c>
+      <c r="P16" s="44">
+        <f>SUM(O11:O16)</f>
+        <v>63969075</v>
+      </c>
+      <c r="S16" s="42">
+        <v>46146</v>
+      </c>
+      <c r="T16" s="44">
+        <v>175000</v>
+      </c>
+      <c r="U16" s="44">
+        <f>SUM(T11:T16)</f>
+        <v>678050</v>
+      </c>
+      <c r="V16" s="44">
+        <f>4672408+7157064+4777940+4179655</f>
+        <v>20787067</v>
+      </c>
+      <c r="W16" s="44">
+        <f>SUM(V11:V16)</f>
+        <v>76043832</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L17" s="42">
+        <v>46202</v>
+      </c>
+      <c r="M17" s="44">
+        <v>150000</v>
+      </c>
+      <c r="N17" s="44">
+        <f>SUM(M11:M17)</f>
+        <v>850000</v>
+      </c>
+      <c r="O17" s="44">
+        <f>2114391+2026527+2118468+2147988+2086704</f>
+        <v>10494078</v>
+      </c>
+      <c r="P17" s="44">
+        <f>SUM(O11:O17)</f>
+        <v>74463153</v>
+      </c>
+      <c r="S17" s="42">
+        <v>46149</v>
+      </c>
+      <c r="T17" s="44">
+        <v>92000</v>
+      </c>
+      <c r="U17" s="44">
+        <f>SUM(T11:T17)</f>
+        <v>770050</v>
+      </c>
+      <c r="V17" s="44">
+        <f>3210424+3522330+4210563</f>
+        <v>10943317</v>
+      </c>
+      <c r="W17" s="44">
+        <f>SUM(V11:V17)</f>
+        <v>86987149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L18" s="42">
+        <v>46209</v>
+      </c>
+      <c r="M18" s="44">
+        <v>150000</v>
+      </c>
+      <c r="N18" s="44">
+        <f>SUM(M11:M18)</f>
+        <v>1000000</v>
+      </c>
+      <c r="O18" s="44">
+        <f>2152629+2223816+2245770+2647461+2763897</f>
+        <v>12033573</v>
+      </c>
+      <c r="P18" s="44">
+        <f>SUM(O11:O18)</f>
+        <v>86496726</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
+      <c r="L19" s="42">
+        <v>46216</v>
+      </c>
+      <c r="M19" s="44">
+        <v>150000</v>
+      </c>
+      <c r="N19" s="44">
+        <f>SUM(M11:M19)</f>
+        <v>1150000</v>
+      </c>
+      <c r="O19" s="44">
+        <f>2629713+2603649+2498823+2477481+2466021</f>
+        <v>12675687</v>
+      </c>
+      <c r="P19" s="44">
+        <f>SUM(O11:O19)</f>
+        <v>99172413</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L20" s="42">
+        <v>46223</v>
+      </c>
+      <c r="M20" s="44">
+        <v>139314</v>
+      </c>
+      <c r="N20" s="44">
+        <f>SUM(M11:M20)</f>
+        <v>1289314</v>
+      </c>
+      <c r="O20" s="44">
+        <f>2425200+2371137+2389767+2052513+2060762</f>
+        <v>11299379</v>
+      </c>
+      <c r="P20" s="44">
+        <f>SUM(O11:O20)</f>
+        <v>110471792</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L21" s="42">
+        <v>46230</v>
+      </c>
+      <c r="M21" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N21" s="44">
+        <f>SUM(M11:M21)</f>
+        <v>1414314</v>
+      </c>
+      <c r="O21" s="44">
+        <f>2172578+2193673+2159755+2098008+2075510</f>
+        <v>10699524</v>
+      </c>
+      <c r="P21" s="44">
+        <f>SUM(O11:O21)</f>
+        <v>121171316</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L22" s="42">
+        <v>46237</v>
+      </c>
+      <c r="M22" s="44">
+        <v>123000</v>
+      </c>
+      <c r="N22" s="44">
+        <f>SUM(M11:M22)</f>
+        <v>1537314</v>
+      </c>
+      <c r="O22" s="44">
+        <f>2144525+2270753+2318220+2203942+2067048</f>
+        <v>11004488</v>
+      </c>
+      <c r="P22" s="44">
+        <f>SUM(O11:O22)</f>
+        <v>132175804</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L23" s="42">
+        <v>46244</v>
+      </c>
+      <c r="M23" s="44">
+        <v>120000</v>
+      </c>
+      <c r="N23" s="44">
+        <f>SUM(M11:M23)</f>
+        <v>1657314</v>
+      </c>
+      <c r="O23" s="44">
+        <f>1993606+1992838+1993927+1976184+2073434</f>
+        <v>10029989</v>
+      </c>
+      <c r="P23" s="44">
+        <f>SUM(O11:O23)</f>
+        <v>142205793</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L24" s="42">
+        <v>46251</v>
+      </c>
+      <c r="M24" s="44">
+        <v>120000</v>
+      </c>
+      <c r="N24" s="44">
+        <f>SUM(M11:M24)</f>
+        <v>1777314</v>
+      </c>
+      <c r="O24" s="44">
+        <f>2115127+2196410+2249364+2290718+2447254</f>
+        <v>11298873</v>
+      </c>
+      <c r="P24" s="44">
+        <f>SUM(O11:O24)</f>
+        <v>153504666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L25" s="42">
+        <v>46258</v>
+      </c>
+      <c r="M25" s="44">
+        <v>233610</v>
+      </c>
+      <c r="N25" s="44">
+        <f>SUM(M11:M25)</f>
+        <v>2010924</v>
+      </c>
+      <c r="O25" s="44">
+        <f>9964430+6154114+2528405+2516355+2465148</f>
+        <v>23628452</v>
+      </c>
+      <c r="P25" s="44">
+        <f>SUM(O11:O25)</f>
+        <v>177133118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L26" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M26" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N26" s="44">
+        <f>SUM(M11:M26)</f>
+        <v>2135924</v>
+      </c>
+      <c r="O26" s="44">
+        <f>2417395+2540775+2513665+2497990+2472325</f>
+        <v>12442150</v>
+      </c>
+      <c r="P26" s="44">
+        <f>SUM(O11:O26)</f>
+        <v>189575268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L27" s="42">
+        <v>46272</v>
+      </c>
+      <c r="M27" s="44">
+        <v>125000</v>
+      </c>
+      <c r="N27" s="44">
+        <f>SUM(M11:M27)</f>
+        <v>2260924</v>
+      </c>
+      <c r="O27" s="44">
+        <f>2413280+2294688+2224273+2258573+2250153</f>
+        <v>11440967</v>
+      </c>
+      <c r="P27" s="44">
+        <f>SUM(O11:O27)</f>
+        <v>201016235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="48">
+        <v>46274</v>
+      </c>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="P28" s="49"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" s="45" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="45" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1022,7 +1990,9 @@
     <col min="15" max="15" width="10.33203125" style="2" customWidth="1"/>
     <col min="16" max="32" width="10.83203125" style="2"/>
     <col min="33" max="33" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="45" width="10.83203125" style="2"/>
+    <col min="34" max="34" width="10.83203125" style="2"/>
+    <col min="35" max="35" width="10.83203125" style="4"/>
+    <col min="36" max="45" width="10.83203125" style="2"/>
     <col min="46" max="46" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="48" max="16384" width="10.83203125" style="2"/>
@@ -1099,16 +2069,16 @@
         <v>36</v>
       </c>
       <c r="T3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="U3" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -1139,7 +2109,7 @@
       <c r="AH3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AI3" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AJ3" s="7" t="s">
@@ -1175,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="20">
-        <v>77.5</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>51</v>
@@ -1231,7 +2201,9 @@
       <c r="T4" s="12">
         <v>247.4</v>
       </c>
-      <c r="U4" s="14"/>
+      <c r="U4" s="12">
+        <v>371.7</v>
+      </c>
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
       <c r="X4" s="12"/>
@@ -1263,45 +2235,45 @@
       <c r="AH4" s="12">
         <v>1528</v>
       </c>
-      <c r="AI4" s="12">
-        <f>AH4*1.02</f>
-        <v>1558.56</v>
+      <c r="AI4" s="13">
+        <f>AH4*0.75</f>
+        <v>1146</v>
       </c>
       <c r="AJ4" s="12">
         <f>AI4*1.05</f>
-        <v>1636.4880000000001</v>
+        <v>1203.3</v>
       </c>
       <c r="AK4" s="12">
         <f t="shared" ref="AK4:AR4" si="0">AJ4*1.05</f>
-        <v>1718.3124</v>
+        <v>1263.4649999999999</v>
       </c>
       <c r="AL4" s="12">
         <f t="shared" si="0"/>
-        <v>1804.22802</v>
+        <v>1326.63825</v>
       </c>
       <c r="AM4" s="12">
         <f t="shared" si="0"/>
-        <v>1894.439421</v>
+        <v>1392.9701625</v>
       </c>
       <c r="AN4" s="12">
         <f t="shared" si="0"/>
-        <v>1989.1613920500001</v>
+        <v>1462.618670625</v>
       </c>
       <c r="AO4" s="12">
         <f t="shared" si="0"/>
-        <v>2088.6194616525004</v>
+        <v>1535.7496041562501</v>
       </c>
       <c r="AP4" s="12">
         <f t="shared" si="0"/>
-        <v>2193.0504347351257</v>
+        <v>1612.5370843640628</v>
       </c>
       <c r="AQ4" s="12">
         <f t="shared" si="0"/>
-        <v>2302.7029564718819</v>
+        <v>1693.1639385822659</v>
       </c>
       <c r="AR4" s="12">
         <f t="shared" si="0"/>
-        <v>2417.8381042954761</v>
+        <v>1777.8221355113792</v>
       </c>
     </row>
     <row r="5" spans="1:206" x14ac:dyDescent="0.25">
@@ -1364,6 +2336,9 @@
       </c>
       <c r="T5" s="14">
         <v>4.4000000000000004</v>
+      </c>
+      <c r="U5" s="14">
+        <v>5</v>
       </c>
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
@@ -1396,7 +2371,7 @@
       <c r="AH5" s="14">
         <v>16</v>
       </c>
-      <c r="AI5" s="14">
+      <c r="AI5" s="15">
         <v>0</v>
       </c>
       <c r="AJ5" s="14">
@@ -1433,7 +2408,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>7363.1468150000001</v>
+        <v>6555.5758740000001</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -1488,6 +2463,9 @@
       </c>
       <c r="T6" s="14">
         <v>-103</v>
+      </c>
+      <c r="U6" s="14">
+        <v>-142.4</v>
       </c>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
@@ -1520,45 +2498,45 @@
       <c r="AH6" s="14">
         <v>-549</v>
       </c>
-      <c r="AI6" s="14">
-        <f>AH6*1.02</f>
-        <v>-559.98</v>
+      <c r="AI6" s="15">
+        <f>AH6*0.85</f>
+        <v>-466.65</v>
       </c>
       <c r="AJ6" s="14">
         <f>AI6*1.05</f>
-        <v>-587.97900000000004</v>
+        <v>-489.98250000000002</v>
       </c>
       <c r="AK6" s="14">
         <f t="shared" ref="AK6:AR6" si="1">AJ6*1.05</f>
-        <v>-617.37795000000006</v>
+        <v>-514.48162500000001</v>
       </c>
       <c r="AL6" s="14">
         <f t="shared" si="1"/>
-        <v>-648.24684750000006</v>
+        <v>-540.20570625000005</v>
       </c>
       <c r="AM6" s="14">
         <f t="shared" si="1"/>
-        <v>-680.65918987500004</v>
+        <v>-567.21599156250011</v>
       </c>
       <c r="AN6" s="14">
         <f t="shared" si="1"/>
-        <v>-714.69214936875005</v>
+        <v>-595.57679114062512</v>
       </c>
       <c r="AO6" s="14">
         <f t="shared" si="1"/>
-        <v>-750.42675683718755</v>
+        <v>-625.35563069765635</v>
       </c>
       <c r="AP6" s="14">
         <f t="shared" si="1"/>
-        <v>-787.94809467904702</v>
+        <v>-656.62341223253918</v>
       </c>
       <c r="AQ6" s="14">
         <f t="shared" si="1"/>
-        <v>-827.3454994129994</v>
+        <v>-689.45458284416623</v>
       </c>
       <c r="AR6" s="14">
         <f t="shared" si="1"/>
-        <v>-868.71277438364939</v>
+        <v>-723.92731198637455</v>
       </c>
     </row>
     <row r="7" spans="1:206" x14ac:dyDescent="0.25">
@@ -1566,8 +2544,8 @@
         <v>45</v>
       </c>
       <c r="B7" s="5">
-        <f>T41</f>
-        <v>113.8</v>
+        <f>U41</f>
+        <v>173.8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>54</v>
@@ -1623,6 +2601,9 @@
       <c r="T7" s="14">
         <v>-59</v>
       </c>
+      <c r="U7" s="14">
+        <v>-62.9</v>
+      </c>
       <c r="Z7" s="14">
         <v>-60.5</v>
       </c>
@@ -1650,45 +2631,45 @@
       <c r="AH7" s="14">
         <v>-226</v>
       </c>
-      <c r="AI7" s="14">
-        <f t="shared" ref="AI7:AI9" si="2">AH7*1.02</f>
-        <v>-230.52</v>
+      <c r="AI7" s="15">
+        <f t="shared" ref="AI7:AI9" si="2">AH7*0.85</f>
+        <v>-192.1</v>
       </c>
       <c r="AJ7" s="14">
         <f t="shared" ref="AJ7:AR9" si="3">AI7*1.05</f>
-        <v>-242.04600000000002</v>
+        <v>-201.70500000000001</v>
       </c>
       <c r="AK7" s="14">
         <f t="shared" si="3"/>
-        <v>-254.14830000000003</v>
+        <v>-211.79025000000001</v>
       </c>
       <c r="AL7" s="14">
         <f t="shared" si="3"/>
-        <v>-266.85571500000003</v>
+        <v>-222.37976250000003</v>
       </c>
       <c r="AM7" s="14">
         <f t="shared" si="3"/>
-        <v>-280.19850075000005</v>
+        <v>-233.49875062500004</v>
       </c>
       <c r="AN7" s="14">
         <f t="shared" si="3"/>
-        <v>-294.20842578750006</v>
+        <v>-245.17368815625005</v>
       </c>
       <c r="AO7" s="14">
         <f t="shared" si="3"/>
-        <v>-308.91884707687507</v>
+        <v>-257.43237256406258</v>
       </c>
       <c r="AP7" s="14">
         <f t="shared" si="3"/>
-        <v>-324.36478943071882</v>
+        <v>-270.3039911922657</v>
       </c>
       <c r="AQ7" s="14">
         <f t="shared" si="3"/>
-        <v>-340.5830289022548</v>
+        <v>-283.81919075187898</v>
       </c>
       <c r="AR7" s="14">
         <f t="shared" si="3"/>
-        <v>-357.61218034736754</v>
+        <v>-298.01015028947296</v>
       </c>
     </row>
     <row r="8" spans="1:206" x14ac:dyDescent="0.25">
@@ -1696,8 +2677,8 @@
         <v>46</v>
       </c>
       <c r="B8" s="5">
-        <f>T45</f>
-        <v>706.8</v>
+        <f>U45</f>
+        <v>846.8</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>55</v>
@@ -1752,6 +2733,9 @@
       </c>
       <c r="T8" s="14">
         <v>-23.9</v>
+      </c>
+      <c r="U8" s="14">
+        <v>-23</v>
       </c>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
@@ -1784,45 +2768,45 @@
       <c r="AH8" s="14">
         <v>-94</v>
       </c>
-      <c r="AI8" s="14">
+      <c r="AI8" s="15">
         <f t="shared" si="2"/>
-        <v>-95.88</v>
+        <v>-79.899999999999991</v>
       </c>
       <c r="AJ8" s="14">
         <f t="shared" si="3"/>
-        <v>-100.67399999999999</v>
+        <v>-83.894999999999996</v>
       </c>
       <c r="AK8" s="14">
         <f t="shared" si="3"/>
-        <v>-105.7077</v>
+        <v>-88.089749999999995</v>
       </c>
       <c r="AL8" s="14">
         <f t="shared" si="3"/>
-        <v>-110.99308500000001</v>
+        <v>-92.494237499999997</v>
       </c>
       <c r="AM8" s="14">
         <f t="shared" si="3"/>
-        <v>-116.54273925000001</v>
+        <v>-97.118949375</v>
       </c>
       <c r="AN8" s="14">
         <f t="shared" si="3"/>
-        <v>-122.36987621250002</v>
+        <v>-101.97489684375</v>
       </c>
       <c r="AO8" s="14">
         <f t="shared" si="3"/>
-        <v>-128.48837002312501</v>
+        <v>-107.0736416859375</v>
       </c>
       <c r="AP8" s="14">
         <f t="shared" si="3"/>
-        <v>-134.91278852428127</v>
+        <v>-112.42732377023438</v>
       </c>
       <c r="AQ8" s="14">
         <f t="shared" si="3"/>
-        <v>-141.65842795049534</v>
+        <v>-118.04868995874611</v>
       </c>
       <c r="AR8" s="14">
         <f t="shared" si="3"/>
-        <v>-148.74134934802012</v>
+        <v>-123.95112445668342</v>
       </c>
     </row>
     <row r="9" spans="1:206" x14ac:dyDescent="0.25">
@@ -1831,7 +2815,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>7956.1468150000001</v>
+        <v>7228.5758740000001</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>56</v>
@@ -1886,6 +2870,9 @@
       </c>
       <c r="T9" s="14">
         <v>-0.5</v>
+      </c>
+      <c r="U9" s="14">
+        <v>0</v>
       </c>
       <c r="V9" s="14"/>
       <c r="W9" s="14"/>
@@ -1918,45 +2905,45 @@
       <c r="AH9" s="14">
         <v>-2</v>
       </c>
-      <c r="AI9" s="14">
+      <c r="AI9" s="15">
         <f t="shared" si="2"/>
-        <v>-2.04</v>
+        <v>-1.7</v>
       </c>
       <c r="AJ9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.1420000000000003</v>
+        <v>-1.7849999999999999</v>
       </c>
       <c r="AK9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.2491000000000003</v>
+        <v>-1.87425</v>
       </c>
       <c r="AL9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.3615550000000005</v>
+        <v>-1.9679625000000001</v>
       </c>
       <c r="AM9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.4796327500000008</v>
+        <v>-2.0663606250000002</v>
       </c>
       <c r="AN9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.6036143875000008</v>
+        <v>-2.1696786562500003</v>
       </c>
       <c r="AO9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.733795106875001</v>
+        <v>-2.2781625890625006</v>
       </c>
       <c r="AP9" s="14">
         <f t="shared" si="3"/>
-        <v>-2.8704848622187513</v>
+        <v>-2.3920707185156256</v>
       </c>
       <c r="AQ9" s="14">
         <f t="shared" si="3"/>
-        <v>-3.0140091053296891</v>
+        <v>-2.5116742544414068</v>
       </c>
       <c r="AR9" s="14">
         <f t="shared" si="3"/>
-        <v>-3.1647095605961737</v>
+        <v>-2.6372579671634773</v>
       </c>
     </row>
     <row r="10" spans="1:206" x14ac:dyDescent="0.25">
@@ -2030,6 +3017,10 @@
       <c r="T10" s="14">
         <f>SUM(T6:T9)</f>
         <v>-186.4</v>
+      </c>
+      <c r="U10" s="14">
+        <f>SUM(U6:U9)</f>
+        <v>-228.3</v>
       </c>
       <c r="V10" s="14"/>
       <c r="W10" s="14"/>
@@ -2071,45 +3062,45 @@
         <f t="shared" ref="AH10:AR10" si="6">SUM(AH6:AH9)</f>
         <v>-871</v>
       </c>
-      <c r="AI10" s="14">
+      <c r="AI10" s="15">
         <f t="shared" si="6"/>
-        <v>-888.42</v>
+        <v>-740.35</v>
       </c>
       <c r="AJ10" s="14">
         <f t="shared" si="6"/>
-        <v>-932.84100000000012</v>
+        <v>-777.36749999999995</v>
       </c>
       <c r="AK10" s="14">
         <f t="shared" si="6"/>
-        <v>-979.48305000000016</v>
+        <v>-816.23587499999996</v>
       </c>
       <c r="AL10" s="14">
         <f t="shared" si="6"/>
-        <v>-1028.4572025</v>
+        <v>-857.04766875000007</v>
       </c>
       <c r="AM10" s="14">
         <f t="shared" si="6"/>
-        <v>-1079.8800626250002</v>
+        <v>-899.90005218750025</v>
       </c>
       <c r="AN10" s="14">
         <f t="shared" si="6"/>
-        <v>-1133.8740657562503</v>
+        <v>-944.89505479687512</v>
       </c>
       <c r="AO10" s="14">
         <f t="shared" si="6"/>
-        <v>-1190.5677690440627</v>
+        <v>-992.13980753671899</v>
       </c>
       <c r="AP10" s="14">
         <f t="shared" si="6"/>
-        <v>-1250.096157496266</v>
+        <v>-1041.7467979135549</v>
       </c>
       <c r="AQ10" s="14">
         <f t="shared" si="6"/>
-        <v>-1312.6009653710792</v>
+        <v>-1093.8341378092327</v>
       </c>
       <c r="AR10" s="14">
         <f t="shared" si="6"/>
-        <v>-1378.2310136396331</v>
+        <v>-1148.5258446996945</v>
       </c>
     </row>
     <row r="11" spans="1:206" x14ac:dyDescent="0.25">
@@ -2183,6 +3174,10 @@
       <c r="T11" s="12">
         <f>T4+T10+T5</f>
         <v>65.400000000000006</v>
+      </c>
+      <c r="U11" s="12">
+        <f>U4+U10+U5</f>
+        <v>148.39999999999998</v>
       </c>
       <c r="V11" s="14"/>
       <c r="W11" s="14"/>
@@ -2224,48 +3219,55 @@
         <f t="shared" ref="AH11:AR11" si="9">AH4+AH10+AH5</f>
         <v>673</v>
       </c>
-      <c r="AI11" s="12">
+      <c r="AI11" s="13">
         <f t="shared" si="9"/>
-        <v>670.14</v>
+        <v>405.65</v>
       </c>
       <c r="AJ11" s="12">
         <f t="shared" si="9"/>
-        <v>703.64699999999993</v>
+        <v>425.9325</v>
       </c>
       <c r="AK11" s="12">
         <f t="shared" si="9"/>
-        <v>738.82934999999986</v>
+        <v>447.22912499999995</v>
       </c>
       <c r="AL11" s="12">
         <f t="shared" si="9"/>
-        <v>775.77081750000002</v>
+        <v>469.5905812499999</v>
       </c>
       <c r="AM11" s="12">
         <f t="shared" si="9"/>
-        <v>814.55935837499987</v>
+        <v>493.07011031249976</v>
       </c>
       <c r="AN11" s="12">
         <f t="shared" si="9"/>
-        <v>855.28732629374986</v>
+        <v>517.72361582812493</v>
       </c>
       <c r="AO11" s="12">
         <f t="shared" si="9"/>
-        <v>898.05169260843763</v>
+        <v>543.60979661953115</v>
       </c>
       <c r="AP11" s="12">
         <f t="shared" si="9"/>
-        <v>942.95427723885973</v>
+        <v>570.79028645050789</v>
       </c>
       <c r="AQ11" s="12">
         <f t="shared" si="9"/>
-        <v>990.10199110080271</v>
+        <v>599.32980077303318</v>
       </c>
       <c r="AR11" s="12">
         <f t="shared" si="9"/>
-        <v>1039.607090655843</v>
+        <v>629.29629081168468</v>
       </c>
     </row>
     <row r="12" spans="1:206" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" s="47">
+        <f>(B8-B7)/U26</f>
+        <v>1.101833660772757</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
@@ -2319,6 +3321,9 @@
       </c>
       <c r="T12" s="14">
         <v>-4.5</v>
+      </c>
+      <c r="U12" s="14">
+        <v>-6.4</v>
       </c>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
@@ -2351,7 +3356,7 @@
       <c r="AH12" s="14">
         <v>-18</v>
       </c>
-      <c r="AI12" s="14">
+      <c r="AI12" s="15">
         <v>0</v>
       </c>
       <c r="AJ12" s="14">
@@ -2451,8 +3456,12 @@
         <v>126.10000000000001</v>
       </c>
       <c r="T13" s="14">
-        <f t="shared" ref="T13" si="12">SUM(T11:T12)</f>
+        <f t="shared" ref="T13:U13" si="12">SUM(T11:T12)</f>
         <v>60.900000000000006</v>
+      </c>
+      <c r="U13" s="14">
+        <f t="shared" si="12"/>
+        <v>141.99999999999997</v>
       </c>
       <c r="V13" s="14"/>
       <c r="W13" s="14"/>
@@ -2494,45 +3503,45 @@
         <f t="shared" ref="AH13:AR13" si="14">SUM(AH11:AH12)</f>
         <v>655</v>
       </c>
-      <c r="AI13" s="14">
+      <c r="AI13" s="15">
         <f t="shared" si="14"/>
-        <v>670.14</v>
+        <v>405.65</v>
       </c>
       <c r="AJ13" s="14">
         <f t="shared" si="14"/>
-        <v>703.64699999999993</v>
+        <v>425.9325</v>
       </c>
       <c r="AK13" s="14">
         <f t="shared" si="14"/>
-        <v>738.82934999999986</v>
+        <v>447.22912499999995</v>
       </c>
       <c r="AL13" s="14">
         <f t="shared" si="14"/>
-        <v>775.77081750000002</v>
+        <v>469.5905812499999</v>
       </c>
       <c r="AM13" s="14">
         <f t="shared" si="14"/>
-        <v>814.55935837499987</v>
+        <v>493.07011031249976</v>
       </c>
       <c r="AN13" s="14">
         <f t="shared" si="14"/>
-        <v>855.28732629374986</v>
+        <v>517.72361582812493</v>
       </c>
       <c r="AO13" s="14">
         <f t="shared" si="14"/>
-        <v>898.05169260843763</v>
+        <v>543.60979661953115</v>
       </c>
       <c r="AP13" s="14">
         <f t="shared" si="14"/>
-        <v>942.95427723885973</v>
+        <v>570.79028645050789</v>
       </c>
       <c r="AQ13" s="14">
         <f t="shared" si="14"/>
-        <v>990.10199110080271</v>
+        <v>599.32980077303318</v>
       </c>
       <c r="AR13" s="14">
         <f t="shared" si="14"/>
-        <v>1039.607090655843</v>
+        <v>629.29629081168468</v>
       </c>
     </row>
     <row r="14" spans="1:206" x14ac:dyDescent="0.25">
@@ -2589,6 +3598,9 @@
       </c>
       <c r="T14" s="14">
         <v>-12.6</v>
+      </c>
+      <c r="U14" s="14">
+        <v>-29.7</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
@@ -2621,45 +3633,45 @@
       <c r="AH14" s="14">
         <v>-136</v>
       </c>
-      <c r="AI14" s="14">
+      <c r="AI14" s="15">
         <f t="shared" ref="AI14:AR14" si="15">AI13*-0.2</f>
-        <v>-134.02799999999999</v>
+        <v>-81.13</v>
       </c>
       <c r="AJ14" s="14">
         <f t="shared" si="15"/>
-        <v>-140.7294</v>
+        <v>-85.186500000000009</v>
       </c>
       <c r="AK14" s="14">
         <f t="shared" si="15"/>
-        <v>-147.76586999999998</v>
+        <v>-89.445824999999999</v>
       </c>
       <c r="AL14" s="14">
         <f t="shared" si="15"/>
-        <v>-155.15416350000001</v>
+        <v>-93.918116249999983</v>
       </c>
       <c r="AM14" s="14">
         <f t="shared" si="15"/>
-        <v>-162.91187167499999</v>
+        <v>-98.614022062499956</v>
       </c>
       <c r="AN14" s="14">
         <f t="shared" si="15"/>
-        <v>-171.05746525874997</v>
+        <v>-103.54472316562499</v>
       </c>
       <c r="AO14" s="14">
         <f t="shared" si="15"/>
-        <v>-179.61033852168754</v>
+        <v>-108.72195932390623</v>
       </c>
       <c r="AP14" s="14">
         <f t="shared" si="15"/>
-        <v>-188.59085544777196</v>
+        <v>-114.15805729010158</v>
       </c>
       <c r="AQ14" s="14">
         <f t="shared" si="15"/>
-        <v>-198.02039822016056</v>
+        <v>-119.86596015460664</v>
       </c>
       <c r="AR14" s="14">
         <f t="shared" si="15"/>
-        <v>-207.92141813116859</v>
+        <v>-125.85925816233694</v>
       </c>
     </row>
     <row r="15" spans="1:206" x14ac:dyDescent="0.25">
@@ -2731,10 +3743,13 @@
         <v>99.9</v>
       </c>
       <c r="T15" s="12">
-        <f t="shared" ref="T15" si="18">SUM(T13:T14)</f>
+        <f t="shared" ref="T15:U15" si="18">SUM(T13:T14)</f>
         <v>48.300000000000004</v>
       </c>
-      <c r="U15" s="14"/>
+      <c r="U15" s="12">
+        <f t="shared" si="18"/>
+        <v>112.29999999999997</v>
+      </c>
       <c r="V15" s="14"/>
       <c r="W15" s="14"/>
       <c r="X15" s="14"/>
@@ -2775,693 +3790,693 @@
         <f t="shared" ref="AH15:AR15" si="20">SUM(AH13:AH14)</f>
         <v>519</v>
       </c>
-      <c r="AI15" s="12">
+      <c r="AI15" s="13">
         <f t="shared" si="20"/>
-        <v>536.11199999999997</v>
+        <v>324.52</v>
       </c>
       <c r="AJ15" s="12">
         <f t="shared" si="20"/>
-        <v>562.91759999999999</v>
+        <v>340.74599999999998</v>
       </c>
       <c r="AK15" s="12">
         <f t="shared" si="20"/>
-        <v>591.06347999999991</v>
+        <v>357.78329999999994</v>
       </c>
       <c r="AL15" s="12">
         <f t="shared" si="20"/>
-        <v>620.61665400000004</v>
+        <v>375.67246499999993</v>
       </c>
       <c r="AM15" s="12">
         <f t="shared" si="20"/>
-        <v>651.64748669999994</v>
+        <v>394.45608824999982</v>
       </c>
       <c r="AN15" s="12">
         <f t="shared" si="20"/>
-        <v>684.22986103499989</v>
+        <v>414.17889266249995</v>
       </c>
       <c r="AO15" s="12">
         <f t="shared" si="20"/>
-        <v>718.44135408675015</v>
+        <v>434.88783729562493</v>
       </c>
       <c r="AP15" s="12">
         <f t="shared" si="20"/>
-        <v>754.36342179108783</v>
+        <v>456.63222916040633</v>
       </c>
       <c r="AQ15" s="12">
         <f t="shared" si="20"/>
-        <v>792.08159288064212</v>
+        <v>479.46384061842656</v>
       </c>
       <c r="AR15" s="12">
         <f t="shared" si="20"/>
-        <v>831.68567252467437</v>
+        <v>503.43703264934777</v>
       </c>
       <c r="AS15" s="12">
         <f>AR15*(1+$AU$19)</f>
-        <v>823.36881579942758</v>
+        <v>498.40266232285427</v>
       </c>
       <c r="AT15" s="12">
         <f t="shared" ref="AT15:DE15" si="21">AS15*(1+$AU$19)</f>
-        <v>815.13512764143331</v>
+        <v>493.41863569962572</v>
       </c>
       <c r="AU15" s="12">
         <f t="shared" si="21"/>
-        <v>806.98377636501903</v>
+        <v>488.48444934262949</v>
       </c>
       <c r="AV15" s="12">
         <f t="shared" si="21"/>
-        <v>798.91393860136884</v>
+        <v>483.59960484920322</v>
       </c>
       <c r="AW15" s="12">
         <f t="shared" si="21"/>
-        <v>790.92479921535516</v>
+        <v>478.76360880071115</v>
       </c>
       <c r="AX15" s="12">
         <f t="shared" si="21"/>
-        <v>783.01555122320156</v>
+        <v>473.97597271270405</v>
       </c>
       <c r="AY15" s="12">
         <f t="shared" si="21"/>
-        <v>775.18539571096949</v>
+        <v>469.23621298557703</v>
       </c>
       <c r="AZ15" s="12">
         <f t="shared" si="21"/>
-        <v>767.4335417538598</v>
+        <v>464.54385085572125</v>
       </c>
       <c r="BA15" s="12">
         <f t="shared" si="21"/>
-        <v>759.7592063363212</v>
+        <v>459.89841234716403</v>
       </c>
       <c r="BB15" s="12">
         <f t="shared" si="21"/>
-        <v>752.16161427295799</v>
+        <v>455.29942822369236</v>
       </c>
       <c r="BC15" s="12">
         <f t="shared" si="21"/>
-        <v>744.63999813022838</v>
+        <v>450.74643394145545</v>
       </c>
       <c r="BD15" s="12">
         <f t="shared" si="21"/>
-        <v>737.19359814892607</v>
+        <v>446.23896960204087</v>
       </c>
       <c r="BE15" s="12">
         <f t="shared" si="21"/>
-        <v>729.82166216743678</v>
+        <v>441.77657990602046</v>
       </c>
       <c r="BF15" s="12">
         <f t="shared" si="21"/>
-        <v>722.52344554576246</v>
+        <v>437.35881410696027</v>
       </c>
       <c r="BG15" s="12">
         <f t="shared" si="21"/>
-        <v>715.29821109030479</v>
+        <v>432.98522596589066</v>
       </c>
       <c r="BH15" s="12">
         <f t="shared" si="21"/>
-        <v>708.14522897940174</v>
+        <v>428.65537370623173</v>
       </c>
       <c r="BI15" s="12">
         <f t="shared" si="21"/>
-        <v>701.06377668960772</v>
+        <v>424.36881996916941</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="21"/>
-        <v>694.05313892271158</v>
+        <v>420.12513176947772</v>
       </c>
       <c r="BK15" s="12">
         <f t="shared" si="21"/>
-        <v>687.11260753348449</v>
+        <v>415.92388045178296</v>
       </c>
       <c r="BL15" s="12">
         <f t="shared" si="21"/>
-        <v>680.24148145814968</v>
+        <v>411.76464164726514</v>
       </c>
       <c r="BM15" s="12">
         <f t="shared" si="21"/>
-        <v>673.43906664356814</v>
+        <v>407.64699523079247</v>
       </c>
       <c r="BN15" s="12">
         <f t="shared" si="21"/>
-        <v>666.70467597713241</v>
+        <v>403.57052527848452</v>
       </c>
       <c r="BO15" s="12">
         <f t="shared" si="21"/>
-        <v>660.03762921736109</v>
+        <v>399.53482002569967</v>
       </c>
       <c r="BP15" s="12">
         <f t="shared" si="21"/>
-        <v>653.43725292518752</v>
+        <v>395.53947182544266</v>
       </c>
       <c r="BQ15" s="12">
         <f t="shared" si="21"/>
-        <v>646.90288039593565</v>
+        <v>391.58407710718825</v>
       </c>
       <c r="BR15" s="12">
         <f t="shared" si="21"/>
-        <v>640.43385159197624</v>
+        <v>387.66823633611637</v>
       </c>
       <c r="BS15" s="12">
         <f t="shared" si="21"/>
-        <v>634.02951307605645</v>
+        <v>383.7915539727552</v>
       </c>
       <c r="BT15" s="12">
         <f t="shared" si="21"/>
-        <v>627.68921794529592</v>
+        <v>379.95363843302766</v>
       </c>
       <c r="BU15" s="12">
         <f t="shared" si="21"/>
-        <v>621.41232576584298</v>
+        <v>376.15410204869738</v>
       </c>
       <c r="BV15" s="12">
         <f t="shared" si="21"/>
-        <v>615.19820250818452</v>
+        <v>372.39256102821042</v>
       </c>
       <c r="BW15" s="12">
         <f t="shared" si="21"/>
-        <v>609.04622048310262</v>
+        <v>368.66863541792833</v>
       </c>
       <c r="BX15" s="12">
         <f t="shared" si="21"/>
-        <v>602.95575827827156</v>
+        <v>364.98194906374903</v>
       </c>
       <c r="BY15" s="12">
         <f t="shared" si="21"/>
-        <v>596.92620069548889</v>
+        <v>361.33212957311156</v>
       </c>
       <c r="BZ15" s="12">
         <f t="shared" si="21"/>
-        <v>590.95693868853402</v>
+        <v>357.71880827738045</v>
       </c>
       <c r="CA15" s="12">
         <f t="shared" si="21"/>
-        <v>585.0473693016487</v>
+        <v>354.14162019460662</v>
       </c>
       <c r="CB15" s="12">
         <f t="shared" si="21"/>
-        <v>579.19689560863219</v>
+        <v>350.60020399266057</v>
       </c>
       <c r="CC15" s="12">
         <f t="shared" si="21"/>
-        <v>573.4049266525459</v>
+        <v>347.09420195273395</v>
       </c>
       <c r="CD15" s="12">
         <f t="shared" si="21"/>
-        <v>567.67087738602038</v>
+        <v>343.62325993320661</v>
       </c>
       <c r="CE15" s="12">
         <f t="shared" si="21"/>
-        <v>561.99416861216014</v>
+        <v>340.18702733387454</v>
       </c>
       <c r="CF15" s="12">
         <f t="shared" si="21"/>
-        <v>556.37422692603855</v>
+        <v>336.78515706053577</v>
       </c>
       <c r="CG15" s="12">
         <f t="shared" si="21"/>
-        <v>550.81048465677816</v>
+        <v>333.41730548993041</v>
       </c>
       <c r="CH15" s="12">
         <f t="shared" si="21"/>
-        <v>545.30237981021037</v>
+        <v>330.08313243503113</v>
       </c>
       <c r="CI15" s="12">
         <f t="shared" si="21"/>
-        <v>539.84935601210827</v>
+        <v>326.78230111068081</v>
       </c>
       <c r="CJ15" s="12">
         <f t="shared" si="21"/>
-        <v>534.45086245198718</v>
+        <v>323.51447809957398</v>
       </c>
       <c r="CK15" s="12">
         <f t="shared" si="21"/>
-        <v>529.10635382746727</v>
+        <v>320.27933331857821</v>
       </c>
       <c r="CL15" s="12">
         <f t="shared" si="21"/>
-        <v>523.8152902891926</v>
+        <v>317.0765399853924</v>
       </c>
       <c r="CM15" s="12">
         <f t="shared" si="21"/>
-        <v>518.57713738630071</v>
+        <v>313.9057745855385</v>
       </c>
       <c r="CN15" s="12">
         <f t="shared" si="21"/>
-        <v>513.39136601243774</v>
+        <v>310.76671683968311</v>
       </c>
       <c r="CO15" s="12">
         <f t="shared" si="21"/>
-        <v>508.25745235231335</v>
+        <v>307.65904967128625</v>
       </c>
       <c r="CP15" s="12">
         <f t="shared" si="21"/>
-        <v>503.17487782879022</v>
+        <v>304.58245917457339</v>
       </c>
       <c r="CQ15" s="12">
         <f t="shared" si="21"/>
-        <v>498.1431290505023</v>
+        <v>301.53663458282767</v>
       </c>
       <c r="CR15" s="12">
         <f t="shared" si="21"/>
-        <v>493.16169775999725</v>
+        <v>298.52126823699939</v>
       </c>
       <c r="CS15" s="12">
         <f t="shared" si="21"/>
-        <v>488.23008078239729</v>
+        <v>295.5360555546294</v>
       </c>
       <c r="CT15" s="12">
         <f t="shared" si="21"/>
-        <v>483.34777997457331</v>
+        <v>292.58069499908311</v>
       </c>
       <c r="CU15" s="12">
         <f t="shared" si="21"/>
-        <v>478.51430217482755</v>
+        <v>289.65488804909228</v>
       </c>
       <c r="CV15" s="12">
         <f t="shared" si="21"/>
-        <v>473.72915915307925</v>
+        <v>286.75833916860137</v>
       </c>
       <c r="CW15" s="12">
         <f t="shared" si="21"/>
-        <v>468.99186756154847</v>
+        <v>283.89075577691534</v>
       </c>
       <c r="CX15" s="12">
         <f t="shared" si="21"/>
-        <v>464.30194888593297</v>
+        <v>281.05184821914617</v>
       </c>
       <c r="CY15" s="12">
         <f t="shared" si="21"/>
-        <v>459.65892939707362</v>
+        <v>278.2413297369547</v>
       </c>
       <c r="CZ15" s="12">
         <f t="shared" si="21"/>
-        <v>455.06234010310288</v>
+        <v>275.45891643958515</v>
       </c>
       <c r="DA15" s="12">
         <f t="shared" si="21"/>
-        <v>450.51171670207185</v>
+        <v>272.70432727518931</v>
       </c>
       <c r="DB15" s="12">
         <f t="shared" si="21"/>
-        <v>446.00659953505112</v>
+        <v>269.97728400243744</v>
       </c>
       <c r="DC15" s="12">
         <f t="shared" si="21"/>
-        <v>441.54653353970059</v>
+        <v>267.27751116241308</v>
       </c>
       <c r="DD15" s="12">
         <f t="shared" si="21"/>
-        <v>437.13106820430357</v>
+        <v>264.60473605078897</v>
       </c>
       <c r="DE15" s="12">
         <f t="shared" si="21"/>
-        <v>432.75975752226054</v>
+        <v>261.95868869028106</v>
       </c>
       <c r="DF15" s="12">
         <f t="shared" ref="DF15:FQ15" si="22">DE15*(1+$AU$19)</f>
-        <v>428.43215994703792</v>
+        <v>259.33910180337824</v>
       </c>
       <c r="DG15" s="12">
         <f t="shared" si="22"/>
-        <v>424.14783834756753</v>
+        <v>256.74571078534444</v>
       </c>
       <c r="DH15" s="12">
         <f t="shared" si="22"/>
-        <v>419.90635996409185</v>
+        <v>254.178253677491</v>
       </c>
       <c r="DI15" s="12">
         <f t="shared" si="22"/>
-        <v>415.70729636445094</v>
+        <v>251.63647114071608</v>
       </c>
       <c r="DJ15" s="12">
         <f t="shared" si="22"/>
-        <v>411.55022340080643</v>
+        <v>249.12010642930892</v>
       </c>
       <c r="DK15" s="12">
         <f t="shared" si="22"/>
-        <v>407.43472116679834</v>
+        <v>246.62890536501584</v>
       </c>
       <c r="DL15" s="12">
         <f t="shared" si="22"/>
-        <v>403.36037395513034</v>
+        <v>244.16261631136567</v>
       </c>
       <c r="DM15" s="12">
         <f t="shared" si="22"/>
-        <v>399.32677021557902</v>
+        <v>241.72099014825201</v>
       </c>
       <c r="DN15" s="12">
         <f t="shared" si="22"/>
-        <v>395.33350251342324</v>
+        <v>239.30378024676949</v>
       </c>
       <c r="DO15" s="12">
         <f t="shared" si="22"/>
-        <v>391.38016748828903</v>
+        <v>236.9107424443018</v>
       </c>
       <c r="DP15" s="12">
         <f t="shared" si="22"/>
-        <v>387.46636581340613</v>
+        <v>234.54163501985877</v>
       </c>
       <c r="DQ15" s="12">
         <f t="shared" si="22"/>
-        <v>383.59170215527206</v>
+        <v>232.1962186696602</v>
       </c>
       <c r="DR15" s="12">
         <f t="shared" si="22"/>
-        <v>379.75578513371931</v>
+        <v>229.8742564829636</v>
       </c>
       <c r="DS15" s="12">
         <f t="shared" si="22"/>
-        <v>375.9582272823821</v>
+        <v>227.57551391813396</v>
       </c>
       <c r="DT15" s="12">
         <f t="shared" si="22"/>
-        <v>372.19864500955828</v>
+        <v>225.29975877895262</v>
       </c>
       <c r="DU15" s="12">
         <f t="shared" si="22"/>
-        <v>368.47665855946269</v>
+        <v>223.04676119116309</v>
       </c>
       <c r="DV15" s="12">
         <f t="shared" si="22"/>
-        <v>364.79189197386808</v>
+        <v>220.81629357925146</v>
       </c>
       <c r="DW15" s="12">
         <f t="shared" si="22"/>
-        <v>361.14397305412939</v>
+        <v>218.60813064345894</v>
       </c>
       <c r="DX15" s="12">
         <f t="shared" si="22"/>
-        <v>357.5325333235881</v>
+        <v>216.42204933702433</v>
       </c>
       <c r="DY15" s="12">
         <f t="shared" si="22"/>
-        <v>353.95720799035223</v>
+        <v>214.2578288436541</v>
       </c>
       <c r="DZ15" s="12">
         <f t="shared" si="22"/>
-        <v>350.41763591044872</v>
+        <v>212.11525055521756</v>
       </c>
       <c r="EA15" s="12">
         <f t="shared" si="22"/>
-        <v>346.91345955134426</v>
+        <v>209.99409804966538</v>
       </c>
       <c r="EB15" s="12">
         <f t="shared" si="22"/>
-        <v>343.44432495583084</v>
+        <v>207.89415706916873</v>
       </c>
       <c r="EC15" s="12">
         <f t="shared" si="22"/>
-        <v>340.00988170627255</v>
+        <v>205.81521549847704</v>
       </c>
       <c r="ED15" s="12">
         <f t="shared" si="22"/>
-        <v>336.60978288920984</v>
+        <v>203.75706334349226</v>
       </c>
       <c r="EE15" s="12">
         <f t="shared" si="22"/>
-        <v>333.24368506031772</v>
+        <v>201.71949271005735</v>
       </c>
       <c r="EF15" s="12">
         <f t="shared" si="22"/>
-        <v>329.91124820971453</v>
+        <v>199.70229778295678</v>
       </c>
       <c r="EG15" s="12">
         <f t="shared" si="22"/>
-        <v>326.61213572761739</v>
+        <v>197.7052748051272</v>
       </c>
       <c r="EH15" s="12">
         <f t="shared" si="22"/>
-        <v>323.34601437034121</v>
+        <v>195.72822205707593</v>
       </c>
       <c r="EI15" s="12">
         <f t="shared" si="22"/>
-        <v>320.11255422663777</v>
+        <v>193.77093983650516</v>
       </c>
       <c r="EJ15" s="12">
         <f t="shared" si="22"/>
-        <v>316.9114286843714</v>
+        <v>191.83323043814011</v>
       </c>
       <c r="EK15" s="12">
         <f t="shared" si="22"/>
-        <v>313.74231439752771</v>
+        <v>189.9148981337587</v>
       </c>
       <c r="EL15" s="12">
         <f t="shared" si="22"/>
-        <v>310.60489125355241</v>
+        <v>188.01574915242111</v>
       </c>
       <c r="EM15" s="12">
         <f t="shared" si="22"/>
-        <v>307.49884234101688</v>
+        <v>186.13559166089689</v>
       </c>
       <c r="EN15" s="12">
         <f t="shared" si="22"/>
-        <v>304.42385391760672</v>
+        <v>184.27423574428792</v>
       </c>
       <c r="EO15" s="12">
         <f t="shared" si="22"/>
-        <v>301.37961537843063</v>
+        <v>182.43149338684503</v>
       </c>
       <c r="EP15" s="12">
         <f t="shared" si="22"/>
-        <v>298.36581922464632</v>
+        <v>180.60717845297657</v>
       </c>
       <c r="EQ15" s="12">
         <f t="shared" si="22"/>
-        <v>295.38216103239984</v>
+        <v>178.80110666844681</v>
       </c>
       <c r="ER15" s="12">
         <f t="shared" si="22"/>
-        <v>292.42833942207585</v>
+        <v>177.01309560176233</v>
       </c>
       <c r="ES15" s="12">
         <f t="shared" si="22"/>
-        <v>289.50405602785509</v>
+        <v>175.24296464574471</v>
       </c>
       <c r="ET15" s="12">
         <f t="shared" si="22"/>
-        <v>286.60901546757651</v>
+        <v>173.49053499928726</v>
       </c>
       <c r="EU15" s="12">
         <f t="shared" si="22"/>
-        <v>283.74292531290075</v>
+        <v>171.75562964929438</v>
       </c>
       <c r="EV15" s="12">
         <f t="shared" si="22"/>
-        <v>280.90549605977174</v>
+        <v>170.03807335280143</v>
       </c>
       <c r="EW15" s="12">
         <f t="shared" si="22"/>
-        <v>278.096441099174</v>
+        <v>168.33769261927341</v>
       </c>
       <c r="EX15" s="12">
         <f t="shared" si="22"/>
-        <v>275.31547668818229</v>
+        <v>166.65431569308069</v>
       </c>
       <c r="EY15" s="12">
         <f t="shared" si="22"/>
-        <v>272.56232192130045</v>
+        <v>164.98777253614989</v>
       </c>
       <c r="EZ15" s="12">
         <f t="shared" si="22"/>
-        <v>269.83669870208746</v>
+        <v>163.33789481078838</v>
       </c>
       <c r="FA15" s="12">
         <f t="shared" si="22"/>
-        <v>267.13833171506656</v>
+        <v>161.70451586268049</v>
       </c>
       <c r="FB15" s="12">
         <f t="shared" si="22"/>
-        <v>264.46694839791587</v>
+        <v>160.08747070405369</v>
       </c>
       <c r="FC15" s="12">
         <f t="shared" si="22"/>
-        <v>261.82227891393671</v>
+        <v>158.48659599701315</v>
       </c>
       <c r="FD15" s="12">
         <f t="shared" si="22"/>
-        <v>259.20405612479732</v>
+        <v>156.90173003704302</v>
       </c>
       <c r="FE15" s="12">
         <f t="shared" si="22"/>
-        <v>256.61201556354933</v>
+        <v>155.33271273667259</v>
       </c>
       <c r="FF15" s="12">
         <f t="shared" si="22"/>
-        <v>254.04589540791383</v>
+        <v>153.77938560930588</v>
       </c>
       <c r="FG15" s="12">
         <f t="shared" si="22"/>
-        <v>251.5054364538347</v>
+        <v>152.24159175321282</v>
       </c>
       <c r="FH15" s="12">
         <f t="shared" si="22"/>
-        <v>248.99038208929636</v>
+        <v>150.71917583568069</v>
       </c>
       <c r="FI15" s="12">
         <f t="shared" si="22"/>
-        <v>246.50047826840338</v>
+        <v>149.21198407732388</v>
       </c>
       <c r="FJ15" s="12">
         <f t="shared" si="22"/>
-        <v>244.03547348571934</v>
+        <v>147.71986423655065</v>
       </c>
       <c r="FK15" s="12">
         <f t="shared" si="22"/>
-        <v>241.59511875086213</v>
+        <v>146.24266559418515</v>
       </c>
       <c r="FL15" s="12">
         <f t="shared" si="22"/>
-        <v>239.1791675633535</v>
+        <v>144.78023893824331</v>
       </c>
       <c r="FM15" s="12">
         <f t="shared" si="22"/>
-        <v>236.78737588771997</v>
+        <v>143.33243654886087</v>
       </c>
       <c r="FN15" s="12">
         <f t="shared" si="22"/>
-        <v>234.41950212884277</v>
+        <v>141.89911218337227</v>
       </c>
       <c r="FO15" s="12">
         <f t="shared" si="22"/>
-        <v>232.07530710755432</v>
+        <v>140.48012106153854</v>
       </c>
       <c r="FP15" s="12">
         <f t="shared" si="22"/>
-        <v>229.75455403647877</v>
+        <v>139.07531985092317</v>
       </c>
       <c r="FQ15" s="12">
         <f t="shared" si="22"/>
-        <v>227.45700849611399</v>
+        <v>137.68456665241393</v>
       </c>
       <c r="FR15" s="12">
         <f t="shared" ref="FR15:GX15" si="23">FQ15*(1+$AU$19)</f>
-        <v>225.18243841115284</v>
+        <v>136.3077209858898</v>
       </c>
       <c r="FS15" s="12">
         <f t="shared" si="23"/>
-        <v>222.93061402704132</v>
+        <v>134.94464377603092</v>
       </c>
       <c r="FT15" s="12">
         <f t="shared" si="23"/>
-        <v>220.70130788677091</v>
+        <v>133.59519733827059</v>
       </c>
       <c r="FU15" s="12">
         <f t="shared" si="23"/>
-        <v>218.4942948079032</v>
+        <v>132.25924536488787</v>
       </c>
       <c r="FV15" s="12">
         <f t="shared" si="23"/>
-        <v>216.30935185982418</v>
+        <v>130.93665291123901</v>
       </c>
       <c r="FW15" s="12">
         <f t="shared" si="23"/>
-        <v>214.14625834122594</v>
+        <v>129.62728638212661</v>
       </c>
       <c r="FX15" s="12">
         <f t="shared" si="23"/>
-        <v>212.0047957578137</v>
+        <v>128.33101351830535</v>
       </c>
       <c r="FY15" s="12">
         <f t="shared" si="23"/>
-        <v>209.88474780023554</v>
+        <v>127.0477033831223</v>
       </c>
       <c r="FZ15" s="12">
         <f t="shared" si="23"/>
-        <v>207.78590032223318</v>
+        <v>125.77722634929107</v>
       </c>
       <c r="GA15" s="12">
         <f t="shared" si="23"/>
-        <v>205.70804131901085</v>
+        <v>124.51945408579816</v>
       </c>
       <c r="GB15" s="12">
         <f t="shared" si="23"/>
-        <v>203.65096090582074</v>
+        <v>123.27425954494018</v>
       </c>
       <c r="GC15" s="12">
         <f t="shared" si="23"/>
-        <v>201.61445129676252</v>
+        <v>122.04151694949077</v>
       </c>
       <c r="GD15" s="12">
         <f t="shared" si="23"/>
-        <v>199.5983067837949</v>
+        <v>120.82110177999586</v>
       </c>
       <c r="GE15" s="12">
         <f t="shared" si="23"/>
-        <v>197.60232371595694</v>
+        <v>119.6128907621959</v>
       </c>
       <c r="GF15" s="12">
         <f t="shared" si="23"/>
-        <v>195.62630047879736</v>
+        <v>118.41676185457395</v>
       </c>
       <c r="GG15" s="12">
         <f t="shared" si="23"/>
-        <v>193.67003747400938</v>
+        <v>117.23259423602821</v>
       </c>
       <c r="GH15" s="12">
         <f t="shared" si="23"/>
-        <v>191.73333709926928</v>
+        <v>116.06026829366792</v>
       </c>
       <c r="GI15" s="12">
         <f t="shared" si="23"/>
-        <v>189.81600372827657</v>
+        <v>114.89966561073123</v>
       </c>
       <c r="GJ15" s="12">
         <f t="shared" si="23"/>
-        <v>187.91784369099381</v>
+        <v>113.75066895462392</v>
       </c>
       <c r="GK15" s="12">
         <f t="shared" si="23"/>
-        <v>186.03866525408387</v>
+        <v>112.61316226507768</v>
       </c>
       <c r="GL15" s="12">
         <f t="shared" si="23"/>
-        <v>184.17827860154301</v>
+        <v>111.4870306424269</v>
       </c>
       <c r="GM15" s="12">
         <f t="shared" si="23"/>
-        <v>182.33649581552757</v>
+        <v>110.37216033600264</v>
       </c>
       <c r="GN15" s="12">
         <f t="shared" si="23"/>
-        <v>180.51313085737229</v>
+        <v>109.26843873264261</v>
       </c>
       <c r="GO15" s="12">
         <f t="shared" si="23"/>
-        <v>178.70799954879857</v>
+        <v>108.17575434531618</v>
       </c>
       <c r="GP15" s="12">
         <f t="shared" si="23"/>
-        <v>176.92091955331057</v>
+        <v>107.09399680186301</v>
       </c>
       <c r="GQ15" s="12">
         <f t="shared" si="23"/>
-        <v>175.15171035777746</v>
+        <v>106.02305683384438</v>
       </c>
       <c r="GR15" s="12">
         <f t="shared" si="23"/>
-        <v>173.40019325419968</v>
+        <v>104.96282626550594</v>
       </c>
       <c r="GS15" s="12">
         <f t="shared" si="23"/>
-        <v>171.66619132165769</v>
+        <v>103.91319800285088</v>
       </c>
       <c r="GT15" s="12">
         <f t="shared" si="23"/>
-        <v>169.94952940844112</v>
+        <v>102.87406602282236</v>
       </c>
       <c r="GU15" s="12">
         <f t="shared" si="23"/>
-        <v>168.25003411435671</v>
+        <v>101.84532536259414</v>
       </c>
       <c r="GV15" s="12">
         <f t="shared" si="23"/>
-        <v>166.56753377321314</v>
+        <v>100.8268721089682</v>
       </c>
       <c r="GW15" s="12">
         <f t="shared" si="23"/>
-        <v>164.90185843548102</v>
+        <v>99.818603387878525</v>
       </c>
       <c r="GX15" s="12">
         <f t="shared" si="23"/>
-        <v>163.2528398511262</v>
+        <v>98.820417353999744</v>
       </c>
     </row>
     <row r="16" spans="1:206" x14ac:dyDescent="0.25">
@@ -3518,6 +4533,9 @@
       </c>
       <c r="T16" s="23">
         <v>93.087464999999995</v>
+      </c>
+      <c r="U16" s="23">
+        <v>91.707931000000002</v>
       </c>
       <c r="V16" s="23"/>
       <c r="W16" s="23"/>
@@ -3550,35 +4568,35 @@
       <c r="AH16" s="23">
         <v>96.146298000000002</v>
       </c>
-      <c r="AI16" s="23">
-        <v>94.058502000000004</v>
+      <c r="AI16" s="5">
+        <v>93.087464999999995</v>
       </c>
       <c r="AJ16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AK16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AL16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AM16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AN16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AO16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AP16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AQ16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
       <c r="AR16" s="23">
-        <v>94.058502000000004</v>
+        <v>93.087464999999995</v>
       </c>
     </row>
     <row r="17" spans="2:47" x14ac:dyDescent="0.25">
@@ -3653,7 +4671,10 @@
         <f>T15/T16</f>
         <v>0.51886685280343603</v>
       </c>
-      <c r="U17" s="24"/>
+      <c r="U17" s="24">
+        <f>U15/U16</f>
+        <v>1.2245396747637887</v>
+      </c>
       <c r="V17" s="24"/>
       <c r="W17" s="24"/>
       <c r="X17" s="24"/>
@@ -3693,45 +4714,45 @@
       <c r="AH17" s="24">
         <v>5.48</v>
       </c>
-      <c r="AI17" s="24">
+      <c r="AI17" s="20">
         <f t="shared" ref="AI17:AR17" si="26">AI15/AI16</f>
-        <v>5.6997718292387853</v>
+        <v>3.4861836660822165</v>
       </c>
       <c r="AJ17" s="24">
         <f t="shared" si="26"/>
-        <v>5.9847604207007246</v>
+        <v>3.6604928493863271</v>
       </c>
       <c r="AK17" s="24">
         <f t="shared" si="26"/>
-        <v>6.2839984417357604</v>
+        <v>3.8435174918556432</v>
       </c>
       <c r="AL17" s="24">
         <f t="shared" si="26"/>
-        <v>6.5981983638225499</v>
+        <v>4.0356933664484256</v>
       </c>
       <c r="AM17" s="24">
         <f t="shared" si="26"/>
-        <v>6.9281082820136763</v>
+        <v>4.2374780347708452</v>
       </c>
       <c r="AN17" s="24">
         <f t="shared" si="26"/>
-        <v>7.2745136961143597</v>
+        <v>4.4493519365093892</v>
       </c>
       <c r="AO17" s="24">
         <f t="shared" si="26"/>
-        <v>7.6382393809200799</v>
+        <v>4.6718195333348582</v>
       </c>
       <c r="AP17" s="24">
         <f t="shared" si="26"/>
-        <v>8.0201513499660866</v>
+        <v>4.9054105100016026</v>
       </c>
       <c r="AQ17" s="24">
         <f t="shared" si="26"/>
-        <v>8.421158917464389</v>
+        <v>5.1506810355016821</v>
       </c>
       <c r="AR17" s="24">
         <f t="shared" si="26"/>
-        <v>8.8422168633376099</v>
+        <v>5.4082150872767647</v>
       </c>
     </row>
     <row r="18" spans="2:47" x14ac:dyDescent="0.25">
@@ -3764,7 +4785,7 @@
       <c r="AF18" s="14"/>
       <c r="AG18" s="14"/>
       <c r="AH18" s="9"/>
-      <c r="AI18" s="9"/>
+      <c r="AI18" s="8"/>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9"/>
       <c r="AL18" s="9"/>
@@ -3775,7 +4796,7 @@
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
       <c r="AT18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AU18" s="31">
         <v>0.08</v>
@@ -3841,6 +4862,10 @@
         <f>(T4-P4)/P4</f>
         <v>-0.24802431610942247</v>
       </c>
+      <c r="U19" s="25">
+        <f>(U4-Q4)/Q4</f>
+        <v>-0.23202479338842977</v>
+      </c>
       <c r="V19" s="25"/>
       <c r="W19" s="25"/>
       <c r="X19" s="25"/>
@@ -3881,48 +4906,48 @@
         <f t="shared" ref="AH19:AR19" si="29">(AH4-AG4)/AG4</f>
         <v>9.4007302928331024E-2</v>
       </c>
-      <c r="AI19" s="25">
+      <c r="AI19" s="27">
         <f t="shared" si="29"/>
-        <v>1.9999999999999966E-2</v>
+        <v>-0.25</v>
       </c>
       <c r="AJ19" s="25">
         <f t="shared" si="29"/>
-        <v>5.0000000000000072E-2</v>
+        <v>4.9999999999999961E-2</v>
       </c>
       <c r="AK19" s="25">
         <f t="shared" si="29"/>
-        <v>4.9999999999999982E-2</v>
+        <v>4.9999999999999975E-2</v>
       </c>
       <c r="AL19" s="25">
         <f t="shared" si="29"/>
-        <v>4.9999999999999996E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM19" s="25">
         <f t="shared" si="29"/>
-        <v>5.000000000000001E-2</v>
+        <v>5.0000000000000037E-2</v>
       </c>
       <c r="AN19" s="25">
         <f t="shared" si="29"/>
-        <v>5.0000000000000051E-2</v>
+        <v>5.0000000000000024E-2</v>
       </c>
       <c r="AO19" s="25">
         <f t="shared" si="29"/>
-        <v>5.0000000000000121E-2</v>
+        <v>5.0000000000000065E-2</v>
       </c>
       <c r="AP19" s="25">
         <f t="shared" si="29"/>
-        <v>5.0000000000000142E-2</v>
+        <v>5.0000000000000114E-2</v>
       </c>
       <c r="AQ19" s="25">
         <f t="shared" si="29"/>
-        <v>4.9999999999999947E-2</v>
+        <v>4.9999999999999982E-2</v>
       </c>
       <c r="AR19" s="25">
         <f t="shared" si="29"/>
-        <v>5.0000000000000072E-2</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="AT19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AU19" s="31">
         <v>-0.01</v>
@@ -3930,7 +4955,7 @@
     </row>
     <row r="20" spans="2:47" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
@@ -3987,6 +5012,10 @@
       <c r="T20" s="25">
         <f>(T10-P10)/P10</f>
         <v>-6.9860279441117765E-2</v>
+      </c>
+      <c r="U20" s="25">
+        <f>(U10-Q10)/Q10</f>
+        <v>-8.0547724526781911E-2</v>
       </c>
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
@@ -4025,52 +5054,52 @@
         <f t="shared" si="31"/>
         <v>0.12590486039296792</v>
       </c>
-      <c r="AI20" s="25">
+      <c r="AI20" s="27">
         <f t="shared" si="31"/>
-        <v>1.9999999999999952E-2</v>
+        <v>-0.14999999999999997</v>
       </c>
       <c r="AJ20" s="25">
         <f t="shared" si="31"/>
-        <v>5.0000000000000183E-2</v>
+        <v>4.9999999999999899E-2</v>
       </c>
       <c r="AK20" s="25">
         <f t="shared" si="31"/>
-        <v>5.0000000000000037E-2</v>
+        <v>5.0000000000000024E-2</v>
       </c>
       <c r="AL20" s="25">
         <f t="shared" si="31"/>
-        <v>4.9999999999999822E-2</v>
+        <v>5.0000000000000135E-2</v>
       </c>
       <c r="AM20" s="25">
         <f t="shared" si="31"/>
-        <v>5.0000000000000162E-2</v>
+        <v>5.0000000000000204E-2</v>
       </c>
       <c r="AN20" s="25">
         <f t="shared" si="31"/>
-        <v>5.0000000000000093E-2</v>
+        <v>4.9999999999999836E-2</v>
       </c>
       <c r="AO20" s="25">
         <f t="shared" si="31"/>
-        <v>4.9999999999999961E-2</v>
+        <v>5.0000000000000128E-2</v>
       </c>
       <c r="AP20" s="25">
         <f t="shared" si="31"/>
-        <v>5.0000000000000065E-2</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="AQ20" s="25">
         <f t="shared" si="31"/>
-        <v>4.999999999999992E-2</v>
+        <v>5.0000000000000065E-2</v>
       </c>
       <c r="AR20" s="25">
         <f t="shared" si="31"/>
-        <v>5.0000000000000024E-2</v>
+        <v>5.0000000000000128E-2</v>
       </c>
       <c r="AT20" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AU20" s="32">
         <f>NPV(AU18,AH15:GX15)</f>
-        <v>8466.5217545136056</v>
+        <v>5314.6308064096011</v>
       </c>
     </row>
     <row r="21" spans="2:47" x14ac:dyDescent="0.25">
@@ -4142,8 +5171,12 @@
         <v>0.37183908045977015</v>
       </c>
       <c r="T21" s="18">
-        <f t="shared" ref="T21" si="34">T11/T4</f>
+        <f t="shared" ref="T21:U21" si="34">T11/T4</f>
         <v>0.26434923201293453</v>
+      </c>
+      <c r="U21" s="18">
+        <f t="shared" si="34"/>
+        <v>0.39924670433145004</v>
       </c>
       <c r="V21" s="18"/>
       <c r="W21" s="18"/>
@@ -4185,51 +5218,51 @@
         <f t="shared" si="35"/>
         <v>0.44044502617801046</v>
       </c>
-      <c r="AI21" s="18">
+      <c r="AI21" s="19">
         <f t="shared" si="35"/>
-        <v>0.42997382198952883</v>
+        <v>0.35397033158813263</v>
       </c>
       <c r="AJ21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952872</v>
+        <v>0.35397033158813263</v>
       </c>
       <c r="AK21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952872</v>
+        <v>0.35397033158813263</v>
       </c>
       <c r="AL21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952883</v>
+        <v>0.35397033158813257</v>
       </c>
       <c r="AM21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952872</v>
+        <v>0.35397033158813246</v>
       </c>
       <c r="AN21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952872</v>
+        <v>0.35397033158813257</v>
       </c>
       <c r="AO21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952877</v>
+        <v>0.35397033158813251</v>
       </c>
       <c r="AP21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952883</v>
+        <v>0.35397033158813263</v>
       </c>
       <c r="AQ21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952883</v>
+        <v>0.35397033158813257</v>
       </c>
       <c r="AR21" s="18">
         <f t="shared" si="35"/>
-        <v>0.42997382198952888</v>
+        <v>0.35397033158813246</v>
       </c>
       <c r="AT21" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="AU21" s="9">
-        <v>95.008346000000003</v>
+      <c r="AU21" s="23">
+        <v>93.087464999999995</v>
       </c>
     </row>
     <row r="22" spans="2:47" x14ac:dyDescent="0.25">
@@ -4274,11 +5307,11 @@
         <v>0.38552094177945062</v>
       </c>
       <c r="AT22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AU22" s="9">
         <f>AU20/AU21</f>
-        <v>89.113452775123619</v>
+        <v>57.092872884760602</v>
       </c>
     </row>
     <row r="23" spans="2:47" x14ac:dyDescent="0.25">
@@ -4311,208 +5344,367 @@
       <c r="AF23" s="18"/>
       <c r="AG23" s="18"/>
       <c r="AT23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU23" s="25">
         <f>(AU22-B4)/B4</f>
-        <v>0.14985100354998218</v>
+        <v>-0.17256705964115068</v>
       </c>
     </row>
     <row r="24" spans="2:47" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="36"/>
       <c r="C24" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
+        <v>109</v>
+      </c>
+      <c r="D24" s="37">
+        <v>85.5</v>
+      </c>
+      <c r="E24" s="37">
+        <v>145</v>
+      </c>
+      <c r="F24" s="37">
+        <v>128.5</v>
+      </c>
+      <c r="G24" s="37">
+        <v>88.8</v>
+      </c>
+      <c r="H24" s="37">
+        <v>87.2</v>
+      </c>
+      <c r="I24" s="37">
+        <v>140.69999999999999</v>
+      </c>
+      <c r="J24" s="37">
+        <v>156</v>
+      </c>
+      <c r="K24" s="37">
+        <v>141.6</v>
+      </c>
+      <c r="L24" s="37">
+        <v>141.6</v>
+      </c>
+      <c r="M24" s="37">
+        <v>216.2</v>
+      </c>
+      <c r="N24" s="37">
+        <v>207.6</v>
+      </c>
+      <c r="O24" s="37">
+        <v>176.3</v>
+      </c>
       <c r="P24" s="37">
         <v>157.5</v>
       </c>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="38"/>
+      <c r="Q24" s="37">
+        <v>260.89999999999998</v>
+      </c>
+      <c r="R24" s="37">
+        <v>195.4</v>
+      </c>
       <c r="S24" s="37">
         <v>153.69999999999999</v>
       </c>
       <c r="T24" s="37">
         <v>89.3</v>
       </c>
-      <c r="V24" s="38"/>
-      <c r="W24" s="38"/>
-      <c r="X24" s="38"/>
-      <c r="Y24" s="38"/>
+      <c r="U24" s="37">
+        <v>172.4</v>
+      </c>
+      <c r="Z24" s="37">
+        <v>108</v>
+      </c>
+      <c r="AA24" s="37">
+        <v>138</v>
+      </c>
+      <c r="AB24" s="37">
+        <v>172</v>
+      </c>
+      <c r="AC24" s="37">
+        <v>202</v>
+      </c>
+      <c r="AD24" s="37">
+        <v>355</v>
+      </c>
+      <c r="AE24" s="37">
+        <v>448</v>
+      </c>
+      <c r="AF24" s="37">
+        <v>526</v>
+      </c>
+      <c r="AG24" s="37">
+        <v>720</v>
+      </c>
+      <c r="AH24" s="37">
+        <v>768</v>
+      </c>
+      <c r="AI24" s="36">
+        <f>AI11-AI8</f>
+        <v>485.54999999999995</v>
+      </c>
+      <c r="AJ24" s="37">
+        <f t="shared" ref="AJ24:AR24" si="36">AJ11-AJ8</f>
+        <v>509.82749999999999</v>
+      </c>
+      <c r="AK24" s="37">
+        <f t="shared" si="36"/>
+        <v>535.31887499999993</v>
+      </c>
+      <c r="AL24" s="37">
+        <f t="shared" si="36"/>
+        <v>562.08481874999984</v>
+      </c>
+      <c r="AM24" s="37">
+        <f t="shared" si="36"/>
+        <v>590.18905968749982</v>
+      </c>
+      <c r="AN24" s="37">
+        <f t="shared" si="36"/>
+        <v>619.69851267187494</v>
+      </c>
+      <c r="AO24" s="37">
+        <f t="shared" si="36"/>
+        <v>650.6834383054686</v>
+      </c>
+      <c r="AP24" s="37">
+        <f t="shared" si="36"/>
+        <v>683.21761022074224</v>
+      </c>
+      <c r="AQ24" s="37">
+        <f t="shared" si="36"/>
+        <v>717.37849073177927</v>
+      </c>
+      <c r="AR24" s="37">
+        <f t="shared" si="36"/>
+        <v>753.24741526836806</v>
+      </c>
     </row>
     <row r="25" spans="2:47" x14ac:dyDescent="0.25">
       <c r="C25" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D25" s="22">
-        <f t="shared" ref="D25:S25" si="36">D24/D4</f>
-        <v>0</v>
+        <f t="shared" ref="D25:S25" si="37">D24/D4</f>
+        <v>0.47473625763464744</v>
       </c>
       <c r="E25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.53604436229205177</v>
       </c>
       <c r="F25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.53541666666666665</v>
       </c>
       <c r="G25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.43960396039603961</v>
       </c>
       <c r="H25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.45774278215223096</v>
       </c>
       <c r="I25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.52421758569299548</v>
       </c>
       <c r="J25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.57205720572057206</v>
       </c>
       <c r="K25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.51341551849166056</v>
       </c>
       <c r="L25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.55748031496062989</v>
       </c>
       <c r="M25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.53303747534516754</v>
       </c>
       <c r="N25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.55716586151368752</v>
       </c>
       <c r="O25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.4836762688614541</v>
       </c>
       <c r="P25" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.47872340425531917</v>
       </c>
       <c r="Q25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.53904958677685944</v>
       </c>
       <c r="R25" s="22">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>0.53213507625272338</v>
       </c>
       <c r="S25" s="22">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.44166666666666665</v>
       </c>
       <c r="T25" s="22">
         <f>T24/T4</f>
         <v>0.36095392077607114</v>
       </c>
-      <c r="U25" s="22"/>
+      <c r="U25" s="22">
+        <f>U24/U4</f>
+        <v>0.46381490449287061</v>
+      </c>
       <c r="V25" s="34"/>
       <c r="W25" s="34"/>
       <c r="X25" s="34"/>
       <c r="Y25" s="34"/>
-      <c r="Z25" s="22"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="22"/>
-      <c r="AC25" s="22"/>
-      <c r="AD25" s="22"/>
-      <c r="AE25" s="22"/>
-      <c r="AF25" s="22"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="22"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="22"/>
-      <c r="AK25" s="22"/>
-      <c r="AL25" s="22"/>
-      <c r="AM25" s="22"/>
-      <c r="AN25" s="22"/>
-      <c r="AO25" s="22"/>
-      <c r="AP25" s="22"/>
-      <c r="AQ25" s="22"/>
-      <c r="AR25" s="22"/>
+      <c r="Z25" s="22">
+        <f t="shared" ref="Z25" si="38">Z24/Z4</f>
+        <v>0.33911610016484806</v>
+      </c>
+      <c r="AA25" s="22">
+        <f t="shared" ref="AA25" si="39">AA24/AA4</f>
+        <v>0.36898395721925131</v>
+      </c>
+      <c r="AB25" s="22">
+        <f t="shared" ref="AB25:AG25" si="40">AB24/AB4</f>
+        <v>0.38533141862450121</v>
+      </c>
+      <c r="AC25" s="22">
+        <f t="shared" si="40"/>
+        <v>0.37006774804615222</v>
+      </c>
+      <c r="AD25" s="22">
+        <f t="shared" si="40"/>
+        <v>0.48636799561583782</v>
+      </c>
+      <c r="AE25" s="22">
+        <f t="shared" si="40"/>
+        <v>0.50235478806907385</v>
+      </c>
+      <c r="AF25" s="22">
+        <f t="shared" si="40"/>
+        <v>0.52234359483614701</v>
+      </c>
+      <c r="AG25" s="22">
+        <f t="shared" si="40"/>
+        <v>0.51550082336937064</v>
+      </c>
+      <c r="AH25" s="22">
+        <f>AH24/AH4</f>
+        <v>0.50261780104712039</v>
+      </c>
+      <c r="AI25" s="46">
+        <f t="shared" ref="AI25:AR25" si="41">AI24/AI4</f>
+        <v>0.42369109947643974</v>
+      </c>
+      <c r="AJ25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643979</v>
+      </c>
+      <c r="AK25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643979</v>
+      </c>
+      <c r="AL25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643968</v>
+      </c>
+      <c r="AM25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643968</v>
+      </c>
+      <c r="AN25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643974</v>
+      </c>
+      <c r="AO25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643963</v>
+      </c>
+      <c r="AP25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643974</v>
+      </c>
+      <c r="AQ25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643968</v>
+      </c>
+      <c r="AR25" s="22">
+        <f t="shared" si="41"/>
+        <v>0.42369109947643963</v>
+      </c>
     </row>
     <row r="26" spans="2:47" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="15"/>
       <c r="C26" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G26" s="14">
-        <f t="shared" ref="G26:S26" si="37">SUM(D24:G24)</f>
-        <v>0</v>
+        <f t="shared" ref="G26:S26" si="42">SUM(D24:G24)</f>
+        <v>447.8</v>
       </c>
       <c r="H26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>449.5</v>
       </c>
       <c r="I26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>445.2</v>
       </c>
       <c r="J26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>472.7</v>
       </c>
       <c r="K26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f>SUM(H24:K24)</f>
+        <v>525.5</v>
       </c>
       <c r="L26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f>SUM(I24:L24)</f>
+        <v>579.9</v>
       </c>
       <c r="M26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>655.40000000000009</v>
       </c>
       <c r="N26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f>SUM(L24:N24)</f>
+        <v>565.4</v>
       </c>
       <c r="O26" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f>SUM(L24:O24)</f>
+        <v>741.7</v>
       </c>
       <c r="P26" s="14">
-        <f t="shared" si="37"/>
-        <v>157.5</v>
+        <f t="shared" si="42"/>
+        <v>757.59999999999991</v>
       </c>
       <c r="Q26" s="14">
-        <f t="shared" si="37"/>
-        <v>157.5</v>
+        <f t="shared" si="42"/>
+        <v>802.3</v>
       </c>
       <c r="R26" s="14">
-        <f t="shared" si="37"/>
-        <v>157.5</v>
+        <f t="shared" si="42"/>
+        <v>790.1</v>
       </c>
       <c r="S26" s="14">
-        <f t="shared" si="37"/>
-        <v>311.2</v>
+        <f t="shared" si="42"/>
+        <v>767.5</v>
       </c>
       <c r="T26" s="14">
         <f>SUM(Q24:T24)</f>
-        <v>243</v>
+        <v>699.3</v>
+      </c>
+      <c r="U26" s="14">
+        <f>SUM(R24:U24)</f>
+        <v>610.80000000000007</v>
       </c>
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
       <c r="X26" s="12"/>
       <c r="Y26" s="12"/>
+      <c r="AI26" s="15"/>
     </row>
     <row r="27" spans="2:47" x14ac:dyDescent="0.25">
       <c r="M27" s="9"/>
@@ -4586,6 +5778,9 @@
       <c r="T28" s="14">
         <v>9109</v>
       </c>
+      <c r="U28" s="14">
+        <v>9095</v>
+      </c>
       <c r="Z28" s="14">
         <v>946</v>
       </c>
@@ -4610,6 +5805,10 @@
       <c r="AG28" s="14">
         <v>6382</v>
       </c>
+      <c r="AH28" s="14">
+        <v>8175</v>
+      </c>
+      <c r="AI28" s="15"/>
     </row>
     <row r="29" spans="2:47" x14ac:dyDescent="0.25">
       <c r="C29" s="2" t="s">
@@ -4620,39 +5819,39 @@
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
       <c r="H29" s="18">
-        <f t="shared" ref="H29:P29" si="38">(H28-D28)/D28</f>
+        <f t="shared" ref="H29:P29" si="43">(H28-D28)/D28</f>
         <v>0.38232002983961211</v>
       </c>
       <c r="I29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.30825165981662977</v>
       </c>
       <c r="J29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.27585193889541715</v>
       </c>
       <c r="K29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.46167161226508407</v>
       </c>
       <c r="L29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.32514840798704803</v>
       </c>
       <c r="M29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.51619139681005322</v>
       </c>
       <c r="N29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.42367027400414459</v>
       </c>
       <c r="O29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.42987650143799694</v>
       </c>
       <c r="P29" s="18">
-        <f t="shared" si="38"/>
+        <f t="shared" si="43"/>
         <v>0.36876399918550196</v>
       </c>
       <c r="Q29" s="18">
@@ -4660,16 +5859,20 @@
         <v>0.34698756773987888</v>
       </c>
       <c r="R29" s="18">
-        <f t="shared" ref="R29:T29" si="39">(R28-N28)/N28</f>
+        <f t="shared" ref="R29:U29" si="44">(R28-N28)/N28</f>
         <v>0.20928351932718744</v>
       </c>
       <c r="S29" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>0.29152863227638431</v>
       </c>
       <c r="T29" s="18">
-        <f t="shared" si="39"/>
+        <f t="shared" si="44"/>
         <v>0.35510264802142222</v>
+      </c>
+      <c r="U29" s="18">
+        <f t="shared" si="44"/>
+        <v>7.6203999526683233E-2</v>
       </c>
       <c r="V29" s="18"/>
       <c r="W29" s="18"/>
@@ -4677,32 +5880,36 @@
       <c r="Y29" s="18"/>
       <c r="Z29" s="18"/>
       <c r="AA29" s="18">
-        <f t="shared" ref="AA29:AF29" si="40">(AA28-Z28)/Z28</f>
+        <f t="shared" ref="AA29:AF29" si="45">(AA28-Z28)/Z28</f>
         <v>0.14059196617336153</v>
       </c>
       <c r="AB29" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0.31047265987025024</v>
       </c>
       <c r="AC29" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0.24469589816124471</v>
       </c>
       <c r="AD29" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0.40170454545454548</v>
       </c>
       <c r="AE29" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0.32752330766112686</v>
       </c>
       <c r="AF29" s="18">
-        <f t="shared" si="40"/>
+        <f t="shared" si="45"/>
         <v>0.37099236641221373</v>
       </c>
       <c r="AG29" s="18">
         <f>(AG28-AF28)/AF28</f>
         <v>0.42138084632516704</v>
+      </c>
+      <c r="AH29" s="18">
+        <f>(AH28-AG28)/AG28</f>
+        <v>0.28094641178314006</v>
       </c>
     </row>
     <row r="30" spans="2:47" x14ac:dyDescent="0.25">
@@ -4737,76 +5944,64 @@
       <c r="AF30" s="21"/>
       <c r="AG30" s="21"/>
     </row>
-    <row r="31" spans="2:47" x14ac:dyDescent="0.25">
-      <c r="C31" s="2" t="s">
+    <row r="31" spans="2:47" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+      <c r="C31" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="14">
         <v>45.7</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="14">
         <v>64.5</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="14">
         <v>52.2</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="14">
         <v>35.799999999999997</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="14">
         <v>36.9</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="14">
         <v>50.6</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="14">
         <v>50.1</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="14">
         <v>37.700000000000003</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="14">
         <v>41.1</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="14">
         <v>55.7</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="14">
         <v>51.5</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31" s="14">
         <v>37.1</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="14">
         <v>41.2</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="14">
         <v>50.5</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="14">
         <v>41.6</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" s="14">
         <v>27.3</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T31" s="14">
         <v>28.6</v>
       </c>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14">
-        <v>215000</v>
-      </c>
-      <c r="AA31" s="14">
-        <v>204000</v>
-      </c>
-      <c r="AB31" s="14">
-        <v>190000</v>
-      </c>
-      <c r="AC31" s="14">
-        <v>189300</v>
+      <c r="U31" s="14">
+        <v>32.9</v>
       </c>
       <c r="AD31" s="14">
         <v>198400</v>
@@ -4820,6 +6015,10 @@
       <c r="AG31" s="14">
         <v>185300</v>
       </c>
+      <c r="AH31" s="14">
+        <v>160700</v>
+      </c>
+      <c r="AI31" s="15"/>
     </row>
     <row r="32" spans="2:47" x14ac:dyDescent="0.25">
       <c r="C32" s="2" t="s">
@@ -4830,39 +6029,39 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:P32" si="41">(H31-D31)/D31</f>
+        <f t="shared" ref="H32:P32" si="46">(H31-D31)/D31</f>
         <v>-0.19256017505470469</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>-0.21550387596899223</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>-4.0229885057471292E-2</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>5.3072625698324188E-2</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>0.11382113821138219</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>0.10079051383399212</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>2.7944111776447077E-2</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>-1.5915119363395264E-2</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="46"/>
         <v>2.4330900243309346E-3</v>
       </c>
       <c r="Q32" s="10">
@@ -4874,41 +6073,44 @@
         <v>-0.19223300970873783</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" ref="S32:T32" si="42">(S31-O31)/O31</f>
+        <f t="shared" ref="S32:U32" si="47">(S31-O31)/O31</f>
         <v>-0.26415094339622641</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="47"/>
         <v>-0.30582524271844663</v>
       </c>
-      <c r="U32" s="18"/>
+      <c r="U32" s="10">
+        <f t="shared" si="47"/>
+        <v>-0.34851485148514855</v>
+      </c>
       <c r="V32" s="10"/>
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
       <c r="Y32" s="18"/>
       <c r="Z32" s="18"/>
-      <c r="AA32" s="18">
-        <f t="shared" ref="AA32:AF32" si="43">(AA31-Z31)/Z31</f>
-        <v>-5.1162790697674418E-2</v>
-      </c>
-      <c r="AB32" s="18">
-        <f t="shared" si="43"/>
-        <v>-6.8627450980392163E-2</v>
-      </c>
-      <c r="AC32" s="18">
-        <f t="shared" si="43"/>
-        <v>-3.6842105263157894E-3</v>
-      </c>
-      <c r="AD32" s="18">
-        <f t="shared" si="43"/>
-        <v>4.8071843634442682E-2</v>
+      <c r="AA32" s="18" t="e">
+        <f t="shared" ref="AA32:AF32" si="48">(AA31-Z31)/Z31</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB32" s="18" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC32" s="18" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD32" s="18" t="e">
+        <f t="shared" si="48"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="AE32" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>-5.0403225806451612E-4</v>
       </c>
       <c r="AF32" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>-0.11598587997982854</v>
       </c>
       <c r="AG32" s="18">
@@ -4916,7 +6118,7 @@
         <v>5.7045065601825443E-2</v>
       </c>
       <c r="AH32" s="18"/>
-      <c r="AI32" s="18"/>
+      <c r="AI32" s="19"/>
       <c r="AJ32" s="18"/>
       <c r="AK32" s="18"/>
       <c r="AL32" s="18"/>
@@ -4927,7 +6129,7 @@
       <c r="AQ32" s="18"/>
       <c r="AR32" s="18"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="18"/>
@@ -4959,7 +6161,7 @@
       <c r="AF33" s="18"/>
       <c r="AG33" s="18"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C34" s="1" t="s">
         <v>49</v>
       </c>
@@ -4977,7 +6179,7 @@
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
     </row>
-    <row r="35" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="4"/>
       <c r="C35" s="2" t="s">
@@ -5034,8 +6236,24 @@
       <c r="T35" s="14">
         <v>902.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U35" s="14">
+        <v>903</v>
+      </c>
+      <c r="AE35" s="14">
+        <v>903</v>
+      </c>
+      <c r="AF35" s="14">
+        <v>903</v>
+      </c>
+      <c r="AG35" s="14">
+        <v>903</v>
+      </c>
+      <c r="AH35" s="14">
+        <v>903</v>
+      </c>
+      <c r="AI35" s="15"/>
+    </row>
+    <row r="36" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="4"/>
       <c r="C36" s="2" t="s">
@@ -5092,8 +6310,24 @@
       <c r="T36" s="14">
         <v>579.29999999999995</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U36" s="14">
+        <v>565.5</v>
+      </c>
+      <c r="AE36" s="14">
+        <v>759.3</v>
+      </c>
+      <c r="AF36" s="14">
+        <v>703.9</v>
+      </c>
+      <c r="AG36" s="14">
+        <v>648.5</v>
+      </c>
+      <c r="AH36" s="14">
+        <v>593.20000000000005</v>
+      </c>
+      <c r="AI36" s="15"/>
+    </row>
+    <row r="37" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="4"/>
       <c r="C37" s="2" t="s">
@@ -5150,12 +6384,28 @@
       <c r="T37" s="14">
         <v>21.7</v>
       </c>
-    </row>
-    <row r="38" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U37" s="14">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AE37" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="AF37" s="14">
+        <v>45.2</v>
+      </c>
+      <c r="AG37" s="14">
+        <v>36.9</v>
+      </c>
+      <c r="AH37" s="14">
+        <v>23.8</v>
+      </c>
+      <c r="AI37" s="15"/>
+    </row>
+    <row r="38" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="4"/>
       <c r="C38" s="2" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="D38" s="14">
         <v>257.5</v>
@@ -5208,12 +6458,28 @@
       <c r="T38" s="14">
         <v>297</v>
       </c>
-    </row>
-    <row r="39" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U38" s="14">
+        <v>297.5</v>
+      </c>
+      <c r="AE38" s="14">
+        <v>263.3</v>
+      </c>
+      <c r="AF38" s="14">
+        <v>292.5</v>
+      </c>
+      <c r="AG38" s="14">
+        <v>297</v>
+      </c>
+      <c r="AH38" s="14">
+        <v>296.8</v>
+      </c>
+      <c r="AI38" s="15"/>
+    </row>
+    <row r="39" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="4"/>
       <c r="C39" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D39" s="14">
         <v>38.200000000000003</v>
@@ -5266,12 +6532,28 @@
       <c r="T39" s="14">
         <v>50.7</v>
       </c>
-    </row>
-    <row r="40" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U39" s="14">
+        <v>75.5</v>
+      </c>
+      <c r="AE39" s="14">
+        <v>31.5</v>
+      </c>
+      <c r="AF39" s="14">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="AG39" s="14">
+        <v>29.8</v>
+      </c>
+      <c r="AH39" s="14">
+        <v>28.9</v>
+      </c>
+      <c r="AI39" s="15"/>
+    </row>
+    <row r="40" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="4"/>
       <c r="C40" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D40" s="14">
         <v>23.3</v>
@@ -5324,12 +6606,28 @@
       <c r="T40" s="14">
         <v>120</v>
       </c>
-    </row>
-    <row r="41" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U40" s="14">
+        <v>77.7</v>
+      </c>
+      <c r="AE40" s="14">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="AF40" s="14">
+        <v>70.7</v>
+      </c>
+      <c r="AG40" s="14">
+        <v>167.2</v>
+      </c>
+      <c r="AH40" s="14">
+        <v>147.6</v>
+      </c>
+      <c r="AI40" s="15"/>
+    </row>
+    <row r="41" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="4"/>
       <c r="C41" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" s="14">
         <v>96.3</v>
@@ -5382,63 +6680,79 @@
       <c r="T41" s="14">
         <v>113.8</v>
       </c>
-    </row>
-    <row r="42" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U41" s="14">
+        <v>173.8</v>
+      </c>
+      <c r="AE41" s="14">
+        <v>100.4</v>
+      </c>
+      <c r="AF41" s="14">
+        <v>102.6</v>
+      </c>
+      <c r="AG41" s="14">
+        <v>111.7</v>
+      </c>
+      <c r="AH41" s="14">
+        <v>103.3</v>
+      </c>
+      <c r="AI41" s="15"/>
+    </row>
+    <row r="42" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="4"/>
       <c r="C42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="12">
-        <f t="shared" ref="D42:P42" si="44">SUM(D35:D41)</f>
+        <f t="shared" ref="D42:P42" si="49">SUM(D35:D41)</f>
         <v>2125.5</v>
       </c>
       <c r="E42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2174.6</v>
       </c>
       <c r="F42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2153.1000000000004</v>
       </c>
       <c r="G42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2094.7999999999997</v>
       </c>
       <c r="H42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2122.8000000000002</v>
       </c>
       <c r="I42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2207.8000000000002</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2215.4999999999995</v>
       </c>
       <c r="K42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2156.1999999999998</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2205.1999999999998</v>
       </c>
       <c r="M42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2251.6999999999998</v>
       </c>
       <c r="N42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2314.8000000000002</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2194.1</v>
       </c>
       <c r="P42" s="12">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>2182.6</v>
       </c>
       <c r="Q42" s="12">
@@ -5446,23 +6760,64 @@
         <v>2239.5</v>
       </c>
       <c r="R42" s="12">
-        <f t="shared" ref="R42:T42" si="45">SUM(R35:R41)</f>
+        <f t="shared" ref="R42:U42" si="50">SUM(R35:R41)</f>
         <v>2268</v>
       </c>
       <c r="S42" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>2096.6</v>
       </c>
       <c r="T42" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>2085.3000000000002</v>
       </c>
-    </row>
-    <row r="43" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U42" s="12">
+        <f t="shared" si="50"/>
+        <v>2111.6</v>
+      </c>
+      <c r="Z42" s="12">
+        <f t="shared" ref="Z42:AD42" si="51">SUM(Z35:Z41)</f>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="12">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AB42" s="12">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AC42" s="12">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AD42" s="12">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="AE42" s="12">
+        <f t="shared" ref="AE42" si="52">SUM(AE35:AE41)</f>
+        <v>2094.7999999999997</v>
+      </c>
+      <c r="AF42" s="12">
+        <f t="shared" ref="AF42" si="53">SUM(AF35:AF41)</f>
+        <v>2156.1999999999998</v>
+      </c>
+      <c r="AG42" s="12">
+        <f t="shared" ref="AG42" si="54">SUM(AG35:AG41)</f>
+        <v>2194.1</v>
+      </c>
+      <c r="AH42" s="12">
+        <f t="shared" ref="AH42" si="55">SUM(AH35:AH41)</f>
+        <v>2096.6</v>
+      </c>
+      <c r="AI42" s="15"/>
+    </row>
+    <row r="43" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="4"/>
       <c r="C43" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D43" s="14">
         <v>1569.4</v>
@@ -5515,63 +6870,79 @@
       <c r="T43" s="14">
         <v>965.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U43" s="14">
+        <v>844.4</v>
+      </c>
+      <c r="AE43" s="14">
+        <v>1432.7</v>
+      </c>
+      <c r="AF43" s="14">
+        <v>1259.5999999999999</v>
+      </c>
+      <c r="AG43" s="14">
+        <v>1248.7</v>
+      </c>
+      <c r="AH43" s="14">
+        <v>1072.2</v>
+      </c>
+      <c r="AI43" s="15"/>
+    </row>
+    <row r="44" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="4"/>
       <c r="C44" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D44" s="26">
-        <f t="shared" ref="D44:P44" si="46">D43</f>
+        <f t="shared" ref="D44:P44" si="56">D43</f>
         <v>1569.4</v>
       </c>
       <c r="E44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1576.1</v>
       </c>
       <c r="F44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1457.4</v>
       </c>
       <c r="G44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1432.7</v>
       </c>
       <c r="H44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1388.9</v>
       </c>
       <c r="I44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1292.2</v>
       </c>
       <c r="J44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1276</v>
       </c>
       <c r="K44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1259.5999999999999</v>
       </c>
       <c r="L44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1216.3</v>
       </c>
       <c r="M44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1197</v>
       </c>
       <c r="N44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1214.2</v>
       </c>
       <c r="O44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1248.7</v>
       </c>
       <c r="P44" s="26">
-        <f t="shared" si="46"/>
+        <f t="shared" si="56"/>
         <v>1232.8</v>
       </c>
       <c r="Q44" s="26">
@@ -5579,23 +6950,64 @@
         <v>1145.2</v>
       </c>
       <c r="R44" s="26">
-        <f t="shared" ref="R44:T44" si="47">R43</f>
+        <f t="shared" ref="R44:U44" si="57">R43</f>
         <v>1129.2</v>
       </c>
       <c r="S44" s="26">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>1072.2</v>
       </c>
       <c r="T44" s="26">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>965.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U44" s="26">
+        <f t="shared" si="57"/>
+        <v>844.4</v>
+      </c>
+      <c r="Z44" s="26">
+        <f t="shared" ref="Z44:AD44" si="58">Z43</f>
+        <v>0</v>
+      </c>
+      <c r="AA44" s="26">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AB44" s="26">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AC44" s="26">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AD44" s="26">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="AE44" s="26">
+        <f t="shared" ref="AE44" si="59">AE43</f>
+        <v>1432.7</v>
+      </c>
+      <c r="AF44" s="26">
+        <f t="shared" ref="AF44" si="60">AF43</f>
+        <v>1259.5999999999999</v>
+      </c>
+      <c r="AG44" s="26">
+        <f t="shared" ref="AG44" si="61">AG43</f>
+        <v>1248.7</v>
+      </c>
+      <c r="AH44" s="26">
+        <f t="shared" ref="AH44" si="62">AH43</f>
+        <v>1072.2</v>
+      </c>
+      <c r="AI44" s="15"/>
+    </row>
+    <row r="45" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="4"/>
       <c r="C45" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D45" s="14">
         <v>213.3</v>
@@ -5648,12 +7060,28 @@
       <c r="T45" s="14">
         <v>706.8</v>
       </c>
-    </row>
-    <row r="46" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U45" s="14">
+        <v>846.8</v>
+      </c>
+      <c r="AE45" s="14">
+        <v>328.5</v>
+      </c>
+      <c r="AF45" s="14">
+        <v>497.1</v>
+      </c>
+      <c r="AG45" s="14">
+        <v>468.5</v>
+      </c>
+      <c r="AH45" s="14">
+        <v>596.9</v>
+      </c>
+      <c r="AI45" s="15"/>
+    </row>
+    <row r="46" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="4"/>
       <c r="C46" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D46" s="14">
         <v>0</v>
@@ -5706,12 +7134,28 @@
       <c r="T46" s="14">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U46" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="AE46" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="14">
+        <v>35.5</v>
+      </c>
+      <c r="AG46" s="14">
+        <v>26</v>
+      </c>
+      <c r="AH46" s="14">
+        <v>13.3</v>
+      </c>
+      <c r="AI46" s="15"/>
+    </row>
+    <row r="47" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="4"/>
       <c r="C47" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D47" s="14">
         <v>217.7</v>
@@ -5764,12 +7208,28 @@
       <c r="T47" s="14">
         <v>179.3</v>
       </c>
-    </row>
-    <row r="48" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U47" s="14">
+        <v>176.5</v>
+      </c>
+      <c r="AE47" s="14">
+        <v>210.2</v>
+      </c>
+      <c r="AF47" s="14">
+        <v>203.7</v>
+      </c>
+      <c r="AG47" s="14">
+        <v>193.5</v>
+      </c>
+      <c r="AH47" s="14">
+        <v>182.1</v>
+      </c>
+      <c r="AI47" s="15"/>
+    </row>
+    <row r="48" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="4"/>
       <c r="C48" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D48" s="26">
         <v>4.5</v>
@@ -5822,12 +7282,28 @@
       <c r="T48" s="14">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="49" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U48" s="14">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AE48" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="14">
+        <v>8.1</v>
+      </c>
+      <c r="AG48" s="14">
+        <v>9.1</v>
+      </c>
+      <c r="AH48" s="14">
+        <v>9.5</v>
+      </c>
+      <c r="AI48" s="15"/>
+    </row>
+    <row r="49" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="4"/>
       <c r="C49" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49" s="14">
         <v>77.7</v>
@@ -5880,12 +7356,28 @@
       <c r="T49" s="14">
         <v>181.1</v>
       </c>
-    </row>
-    <row r="50" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U49" s="14">
+        <v>190.5</v>
+      </c>
+      <c r="AE49" s="14">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="AF49" s="14">
+        <v>110.9</v>
+      </c>
+      <c r="AG49" s="14">
+        <v>193.6</v>
+      </c>
+      <c r="AH49" s="14">
+        <v>177.2</v>
+      </c>
+      <c r="AI49" s="15"/>
+    </row>
+    <row r="50" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="4"/>
       <c r="C50" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D50" s="14">
         <v>42.7</v>
@@ -5938,63 +7430,79 @@
       <c r="T50" s="14">
         <v>33</v>
       </c>
-    </row>
-    <row r="51" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U50" s="14">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="AE50" s="14">
+        <v>42.1</v>
+      </c>
+      <c r="AF50" s="14">
+        <v>41.1</v>
+      </c>
+      <c r="AG50" s="14">
+        <v>54.5</v>
+      </c>
+      <c r="AH50" s="14">
+        <v>46.2</v>
+      </c>
+      <c r="AI50" s="15"/>
+    </row>
+    <row r="51" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="4"/>
       <c r="C51" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" s="26">
-        <f t="shared" ref="D51:P51" si="48">SUM(D45:D50)</f>
+        <f t="shared" ref="D51:P51" si="63">SUM(D45:D50)</f>
         <v>555.90000000000009</v>
       </c>
       <c r="E51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>598.29999999999995</v>
       </c>
       <c r="F51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>695.39999999999986</v>
       </c>
       <c r="G51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>661.90000000000009</v>
       </c>
       <c r="H51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>733.6</v>
       </c>
       <c r="I51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>915.39999999999986</v>
       </c>
       <c r="J51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>939.3</v>
       </c>
       <c r="K51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>896.4</v>
       </c>
       <c r="L51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>988.69999999999993</v>
       </c>
       <c r="M51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>1054.7</v>
       </c>
       <c r="N51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>1100.9999999999998</v>
       </c>
       <c r="O51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>945.2</v>
       </c>
       <c r="P51" s="26">
-        <f t="shared" si="48"/>
+        <f t="shared" si="63"/>
         <v>949.60000000000014</v>
       </c>
       <c r="Q51" s="26">
@@ -6002,74 +7510,115 @@
         <v>1094.3</v>
       </c>
       <c r="R51" s="26">
-        <f t="shared" ref="R51:S51" si="49">SUM(R45:R50)</f>
+        <f t="shared" ref="R51:S51" si="64">SUM(R45:R50)</f>
         <v>1138.8000000000002</v>
       </c>
       <c r="S51" s="26">
-        <f t="shared" si="49"/>
+        <f t="shared" si="64"/>
         <v>1025.2</v>
       </c>
       <c r="T51" s="26">
-        <f t="shared" ref="T51" si="50">SUM(T45:T50)</f>
+        <f t="shared" ref="T51:U51" si="65">SUM(T45:T50)</f>
         <v>1119.8</v>
       </c>
-    </row>
-    <row r="52" spans="1:33" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U51" s="26">
+        <f t="shared" si="65"/>
+        <v>1267</v>
+      </c>
+      <c r="Z51" s="26">
+        <f t="shared" ref="Z51" si="66">SUM(Z45:Z50)</f>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="26">
+        <f t="shared" ref="AA51:AD51" si="67">SUM(AA45:AA50)</f>
+        <v>0</v>
+      </c>
+      <c r="AB51" s="26">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AC51" s="26">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AD51" s="26">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="AE51" s="26">
+        <f t="shared" ref="AE51" si="68">SUM(AE45:AE50)</f>
+        <v>661.90000000000009</v>
+      </c>
+      <c r="AF51" s="26">
+        <f t="shared" ref="AF51" si="69">SUM(AF45:AF50)</f>
+        <v>896.4</v>
+      </c>
+      <c r="AG51" s="26">
+        <f t="shared" ref="AG51" si="70">SUM(AG45:AG50)</f>
+        <v>945.2</v>
+      </c>
+      <c r="AH51" s="26">
+        <f t="shared" ref="AH51" si="71">SUM(AH45:AH50)</f>
+        <v>1025.2</v>
+      </c>
+      <c r="AI51" s="15"/>
+    </row>
+    <row r="52" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="4"/>
       <c r="C52" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D52" s="12">
-        <f t="shared" ref="D52:P52" si="51">D44+D51</f>
+        <f t="shared" ref="D52:P52" si="72">D44+D51</f>
         <v>2125.3000000000002</v>
       </c>
       <c r="E52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2174.3999999999996</v>
       </c>
       <c r="F52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2152.8000000000002</v>
       </c>
       <c r="G52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2094.6000000000004</v>
       </c>
       <c r="H52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2122.5</v>
       </c>
       <c r="I52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2207.6</v>
       </c>
       <c r="J52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2215.3000000000002</v>
       </c>
       <c r="K52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2156</v>
       </c>
       <c r="L52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2205</v>
       </c>
       <c r="M52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2251.6999999999998</v>
       </c>
       <c r="N52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2315.1999999999998</v>
       </c>
       <c r="O52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2193.9</v>
       </c>
       <c r="P52" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="72"/>
         <v>2182.4</v>
       </c>
       <c r="Q52" s="12">
@@ -6077,136 +7626,185 @@
         <v>2239.5</v>
       </c>
       <c r="R52" s="12">
-        <f t="shared" ref="R52:S52" si="52">R44+R51</f>
+        <f t="shared" ref="R52:S52" si="73">R44+R51</f>
         <v>2268</v>
       </c>
       <c r="S52" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="73"/>
         <v>2097.4</v>
       </c>
       <c r="T52" s="12">
-        <f t="shared" ref="T52" si="53">T44+T51</f>
+        <f t="shared" ref="T52:U52" si="74">T44+T51</f>
         <v>2085.3000000000002</v>
       </c>
-    </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="U52" s="12">
+        <f t="shared" si="74"/>
+        <v>2111.4</v>
+      </c>
+      <c r="Z52" s="12">
+        <f t="shared" ref="Z52" si="75">Z44+Z51</f>
+        <v>0</v>
+      </c>
+      <c r="AA52" s="12">
+        <f t="shared" ref="AA52:AD52" si="76">AA44+AA51</f>
+        <v>0</v>
+      </c>
+      <c r="AB52" s="12">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="AC52" s="12">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="AD52" s="12">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="AE52" s="12">
+        <f t="shared" ref="AE52" si="77">AE44+AE51</f>
+        <v>2094.6000000000004</v>
+      </c>
+      <c r="AF52" s="12">
+        <f t="shared" ref="AF52" si="78">AF44+AF51</f>
+        <v>2156</v>
+      </c>
+      <c r="AG52" s="12">
+        <f t="shared" ref="AG52" si="79">AG44+AG51</f>
+        <v>2193.9</v>
+      </c>
+      <c r="AH52" s="12">
+        <f t="shared" ref="AH52" si="80">AH44+AH51</f>
+        <v>2097.4</v>
+      </c>
+      <c r="AI52" s="15"/>
+    </row>
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C54" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="4"/>
       <c r="C55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="14">
+        <f t="shared" ref="D55:U55" si="81">D11</f>
+        <v>68.099999999999994</v>
+      </c>
+      <c r="E55" s="14">
+        <f t="shared" si="81"/>
+        <v>127.80000000000001</v>
+      </c>
+      <c r="F55" s="14">
+        <f t="shared" si="81"/>
+        <v>111.8</v>
+      </c>
+      <c r="G55" s="14">
+        <f t="shared" si="81"/>
+        <v>72.100000000000009</v>
+      </c>
+      <c r="H55" s="14">
+        <f t="shared" si="81"/>
+        <v>68.099999999999994</v>
+      </c>
+      <c r="I55" s="14">
+        <f t="shared" si="81"/>
+        <v>122.09999999999998</v>
+      </c>
+      <c r="J55" s="14">
+        <f t="shared" si="81"/>
+        <v>137.29999999999998</v>
+      </c>
+      <c r="K55" s="14">
+        <f t="shared" si="81"/>
+        <v>121.4</v>
+      </c>
+      <c r="L55" s="14">
+        <f t="shared" si="81"/>
+        <v>98.899999999999977</v>
+      </c>
+      <c r="M55" s="14">
+        <f t="shared" si="81"/>
+        <v>195.60000000000002</v>
+      </c>
+      <c r="N55" s="14">
+        <f t="shared" si="81"/>
+        <v>185.7</v>
+      </c>
+      <c r="O55" s="14">
+        <f t="shared" si="81"/>
+        <v>153.60000000000002</v>
+      </c>
+      <c r="P55" s="14">
+        <f t="shared" si="81"/>
+        <v>135</v>
+      </c>
+      <c r="Q55" s="14">
+        <f t="shared" si="81"/>
+        <v>237.70000000000005</v>
+      </c>
+      <c r="R55" s="14">
+        <f t="shared" si="81"/>
+        <v>171.29999999999998</v>
+      </c>
+      <c r="S55" s="14">
+        <f t="shared" si="81"/>
+        <v>129.4</v>
+      </c>
+      <c r="T55" s="14">
+        <f t="shared" si="81"/>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="U55" s="14">
+        <f t="shared" si="81"/>
+        <v>148.39999999999998</v>
+      </c>
+      <c r="Z55" s="14">
+        <f t="shared" ref="Z55:AH55" si="82">Z11</f>
+        <v>13.19500000000005</v>
+      </c>
+      <c r="AA55" s="14">
+        <f t="shared" si="82"/>
+        <v>72.569999999999993</v>
+      </c>
+      <c r="AB55" s="14">
+        <f t="shared" si="82"/>
+        <v>98.790000000000063</v>
+      </c>
+      <c r="AC55" s="14">
+        <f t="shared" si="82"/>
+        <v>110.53500000000005</v>
+      </c>
+      <c r="AD55" s="14">
+        <f t="shared" si="82"/>
+        <v>223.9</v>
+      </c>
+      <c r="AE55" s="14">
+        <f t="shared" si="82"/>
+        <v>377.5</v>
+      </c>
+      <c r="AF55" s="14">
+        <f t="shared" si="82"/>
+        <v>447.80000000000007</v>
+      </c>
+      <c r="AG55" s="14">
+        <f t="shared" si="82"/>
+        <v>633.80000000000007</v>
+      </c>
+      <c r="AH55" s="14">
+        <f t="shared" si="82"/>
+        <v>673</v>
+      </c>
+      <c r="AI55" s="15"/>
+    </row>
+    <row r="56" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="D55" s="14">
-        <f t="shared" ref="D55:T55" si="54">D11</f>
-        <v>68.099999999999994</v>
-      </c>
-      <c r="E55" s="14">
-        <f t="shared" si="54"/>
-        <v>127.80000000000001</v>
-      </c>
-      <c r="F55" s="14">
-        <f t="shared" si="54"/>
-        <v>111.8</v>
-      </c>
-      <c r="G55" s="14">
-        <f t="shared" si="54"/>
-        <v>72.100000000000009</v>
-      </c>
-      <c r="H55" s="14">
-        <f t="shared" si="54"/>
-        <v>68.099999999999994</v>
-      </c>
-      <c r="I55" s="14">
-        <f t="shared" si="54"/>
-        <v>122.09999999999998</v>
-      </c>
-      <c r="J55" s="14">
-        <f t="shared" si="54"/>
-        <v>137.29999999999998</v>
-      </c>
-      <c r="K55" s="14">
-        <f t="shared" si="54"/>
-        <v>121.4</v>
-      </c>
-      <c r="L55" s="14">
-        <f t="shared" si="54"/>
-        <v>98.899999999999977</v>
-      </c>
-      <c r="M55" s="14">
-        <f t="shared" si="54"/>
-        <v>195.60000000000002</v>
-      </c>
-      <c r="N55" s="14">
-        <f t="shared" si="54"/>
-        <v>185.7</v>
-      </c>
-      <c r="O55" s="14">
-        <f t="shared" si="54"/>
-        <v>153.60000000000002</v>
-      </c>
-      <c r="P55" s="14">
-        <f t="shared" si="54"/>
-        <v>135</v>
-      </c>
-      <c r="Q55" s="14">
-        <f t="shared" si="54"/>
-        <v>237.70000000000005</v>
-      </c>
-      <c r="R55" s="14">
-        <f t="shared" si="54"/>
-        <v>171.29999999999998</v>
-      </c>
-      <c r="S55" s="14">
-        <f t="shared" si="54"/>
-        <v>129.4</v>
-      </c>
-      <c r="T55" s="14">
-        <f t="shared" si="54"/>
-        <v>65.400000000000006</v>
-      </c>
-      <c r="U55" s="14"/>
-      <c r="V55" s="14"/>
-      <c r="W55" s="14"/>
-      <c r="X55" s="14"/>
-      <c r="Y55" s="14"/>
-      <c r="Z55" s="14">
-        <f t="shared" ref="Z55:AG55" si="55">Z11</f>
-        <v>13.19500000000005</v>
-      </c>
-      <c r="AA55" s="14">
-        <f t="shared" si="55"/>
-        <v>72.569999999999993</v>
-      </c>
-      <c r="AB55" s="14">
-        <f t="shared" si="55"/>
-        <v>98.790000000000063</v>
-      </c>
-      <c r="AC55" s="14">
-        <f t="shared" si="55"/>
-        <v>110.53500000000005</v>
-      </c>
-      <c r="AD55" s="14">
-        <f t="shared" si="55"/>
-        <v>223.9</v>
-      </c>
-      <c r="AE55" s="14">
-        <f t="shared" si="55"/>
-        <v>377.5</v>
-      </c>
-      <c r="AF55" s="14">
-        <f t="shared" si="55"/>
-        <v>447.80000000000007</v>
-      </c>
-      <c r="AG55" s="14">
-        <f t="shared" si="55"/>
-        <v>633.80000000000007</v>
-      </c>
-    </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="C56" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D56" s="14">
         <v>68</v>
@@ -6259,11 +7857,9 @@
       <c r="T56" s="14">
         <v>65</v>
       </c>
-      <c r="U56" s="14"/>
-      <c r="V56" s="14"/>
-      <c r="W56" s="14"/>
-      <c r="X56" s="14"/>
-      <c r="Y56" s="14"/>
+      <c r="U56" s="14">
+        <v>149</v>
+      </c>
       <c r="Z56" s="14">
         <v>13</v>
       </c>
@@ -6288,10 +7884,16 @@
       <c r="AG56" s="14">
         <v>634</v>
       </c>
-    </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH56" s="14">
+        <v>673</v>
+      </c>
+      <c r="AI56" s="15"/>
+    </row>
+    <row r="57" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
+      <c r="B57" s="4"/>
       <c r="C57" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D57" s="14">
         <v>17.7</v>
@@ -6344,11 +7946,9 @@
       <c r="T57" s="14">
         <v>24.1</v>
       </c>
-      <c r="U57" s="14"/>
-      <c r="V57" s="14"/>
-      <c r="W57" s="14"/>
-      <c r="X57" s="14"/>
-      <c r="Y57" s="14"/>
+      <c r="U57" s="14">
+        <v>22.7</v>
+      </c>
       <c r="Z57" s="14">
         <v>63.3</v>
       </c>
@@ -6373,10 +7973,17 @@
       <c r="AG57" s="14">
         <v>86</v>
       </c>
-    </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH57" s="14">
+        <f>93.7+1.2+1.3</f>
+        <v>96.2</v>
+      </c>
+      <c r="AI57" s="15"/>
+    </row>
+    <row r="58" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="4"/>
       <c r="C58" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D58" s="14">
         <v>-1.2</v>
@@ -6429,11 +8036,9 @@
       <c r="T58" s="14">
         <v>-4.7</v>
       </c>
-      <c r="U58" s="14"/>
-      <c r="V58" s="14"/>
-      <c r="W58" s="14"/>
-      <c r="X58" s="14"/>
-      <c r="Y58" s="14"/>
+      <c r="U58" s="14">
+        <v>-6.3</v>
+      </c>
       <c r="Z58" s="14">
         <v>-10</v>
       </c>
@@ -6464,10 +8069,16 @@
         <f>3.3-28.6</f>
         <v>-25.3</v>
       </c>
-    </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH58" s="14">
+        <v>-20.399999999999999</v>
+      </c>
+      <c r="AI58" s="15"/>
+    </row>
+    <row r="59" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="4"/>
       <c r="C59" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D59" s="14">
         <v>-26.9</v>
@@ -6520,11 +8131,9 @@
       <c r="T59" s="14">
         <v>-34.700000000000003</v>
       </c>
-      <c r="U59" s="14"/>
-      <c r="V59" s="14"/>
-      <c r="W59" s="14"/>
-      <c r="X59" s="14"/>
-      <c r="Y59" s="14"/>
+      <c r="U59" s="14">
+        <v>-33.5</v>
+      </c>
       <c r="Z59" s="14">
         <v>-22.2</v>
       </c>
@@ -6549,10 +8158,16 @@
       <c r="AG59" s="14">
         <v>-127.7</v>
       </c>
-    </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH59" s="14">
+        <v>-155.1</v>
+      </c>
+      <c r="AI59" s="15"/>
+    </row>
+    <row r="60" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2"/>
+      <c r="B60" s="4"/>
       <c r="C60" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D60" s="14">
         <v>15.3</v>
@@ -6605,11 +8220,9 @@
       <c r="T60" s="14">
         <v>15.8</v>
       </c>
-      <c r="U60" s="14"/>
-      <c r="V60" s="14"/>
-      <c r="W60" s="14"/>
-      <c r="X60" s="14"/>
-      <c r="Y60" s="14"/>
+      <c r="U60" s="14">
+        <v>31.8</v>
+      </c>
       <c r="Z60" s="14">
         <v>16</v>
       </c>
@@ -6634,61 +8247,68 @@
       <c r="AG60" s="14">
         <v>-0.3</v>
       </c>
-    </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH60" s="14">
+        <f>20.5-17</f>
+        <v>3.5</v>
+      </c>
+      <c r="AI60" s="15"/>
+    </row>
+    <row r="61" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="4"/>
       <c r="C61" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D61" s="12">
-        <f t="shared" ref="D61:P61" si="56">SUM(D56:D60)</f>
+        <f t="shared" ref="D61:P61" si="83">SUM(D56:D60)</f>
         <v>72.900000000000006</v>
       </c>
       <c r="E61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>141.79999999999998</v>
       </c>
       <c r="F61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>110.69999999999997</v>
       </c>
       <c r="G61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>32.199999999999996</v>
       </c>
       <c r="H61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>73.599999999999994</v>
       </c>
       <c r="I61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>126.00000000000001</v>
       </c>
       <c r="J61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>129</v>
       </c>
       <c r="K61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>68.09999999999998</v>
       </c>
       <c r="L61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>90.59999999999998</v>
       </c>
       <c r="M61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>204.8</v>
       </c>
       <c r="N61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>132.20000000000002</v>
       </c>
       <c r="O61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>140.1</v>
       </c>
       <c r="P61" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="83"/>
         <v>120.69999999999999</v>
       </c>
       <c r="Q61" s="12">
@@ -6696,90 +8316,75 @@
         <v>229.50000000000003</v>
       </c>
       <c r="R61" s="12">
-        <f t="shared" ref="R61:T61" si="57">SUM(R56:R60)</f>
+        <f t="shared" ref="R61:U61" si="84">SUM(R56:R60)</f>
         <v>242.7</v>
       </c>
       <c r="S61" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="84"/>
         <v>74.600000000000009</v>
       </c>
       <c r="T61" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="84"/>
         <v>65.499999999999986</v>
       </c>
-      <c r="U61" s="14"/>
+      <c r="U61" s="12">
+        <f t="shared" si="84"/>
+        <v>163.69999999999999</v>
+      </c>
       <c r="V61" s="12"/>
       <c r="W61" s="12"/>
       <c r="X61" s="12"/>
       <c r="Y61" s="12"/>
       <c r="Z61" s="12">
-        <f t="shared" ref="Z61:AF61" si="58">SUM(Z56:Z60)</f>
+        <f t="shared" ref="Z61:AF61" si="85">SUM(Z56:Z60)</f>
         <v>60.099999999999994</v>
       </c>
       <c r="AA61" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="85"/>
         <v>90.7</v>
       </c>
       <c r="AB61" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="85"/>
         <v>139.19999999999999</v>
       </c>
       <c r="AC61" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="85"/>
         <v>127.36499999999997</v>
       </c>
       <c r="AD61" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="85"/>
         <v>235.1</v>
       </c>
       <c r="AE61" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="85"/>
         <v>356.5</v>
       </c>
       <c r="AF61" s="12">
-        <f t="shared" si="58"/>
+        <f t="shared" si="85"/>
         <v>395.90000000000003</v>
       </c>
       <c r="AG61" s="12">
         <f>SUM(AG56:AG60)</f>
         <v>566.70000000000005</v>
       </c>
-    </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH61" s="12">
+        <f>SUM(AH56:AH60)</f>
+        <v>597.20000000000005</v>
+      </c>
+      <c r="AI61" s="15"/>
+    </row>
+    <row r="62" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="2"/>
       <c r="D62" s="12"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
-      <c r="Z62" s="14"/>
-      <c r="AA62" s="14"/>
-      <c r="AB62" s="14"/>
-      <c r="AC62" s="14"/>
-      <c r="AD62" s="14"/>
-      <c r="AE62" s="14"/>
-      <c r="AF62" s="14"/>
-      <c r="AG62" s="14"/>
-    </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AI62" s="15"/>
+    </row>
+    <row r="63" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="4"/>
       <c r="C63" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D63" s="14">
         <v>-4</v>
@@ -6832,11 +8437,9 @@
       <c r="T63" s="14">
         <v>-7.1</v>
       </c>
-      <c r="U63" s="14"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="14"/>
-      <c r="X63" s="14"/>
-      <c r="Y63" s="14"/>
+      <c r="U63" s="14">
+        <v>-7</v>
+      </c>
       <c r="Z63" s="14">
         <v>-1457.354</v>
       </c>
@@ -6861,61 +8464,67 @@
       <c r="AG63" s="14">
         <v>-23.5</v>
       </c>
-    </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH63" s="14">
+        <v>-25.7</v>
+      </c>
+      <c r="AI63" s="15"/>
+    </row>
+    <row r="64" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="4"/>
       <c r="C64" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D64" s="12">
-        <f t="shared" ref="D64:P64" si="59">D63</f>
+        <f t="shared" ref="D64:P64" si="86">D63</f>
         <v>-4</v>
       </c>
       <c r="E64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-4.0999999999999996</v>
       </c>
       <c r="F64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-2.2999999999999998</v>
       </c>
       <c r="G64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-5.0999999999999996</v>
       </c>
       <c r="H64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-15</v>
       </c>
       <c r="I64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-7.8</v>
       </c>
       <c r="J64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-7.5</v>
       </c>
       <c r="K64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-8.5</v>
       </c>
       <c r="L64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-8.1</v>
       </c>
       <c r="M64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-6.7</v>
       </c>
       <c r="N64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-3.2</v>
       </c>
       <c r="O64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-5.5</v>
       </c>
       <c r="P64" s="12">
-        <f t="shared" si="59"/>
+        <f t="shared" si="86"/>
         <v>-9.5</v>
       </c>
       <c r="Q64" s="12">
@@ -6923,90 +8532,81 @@
         <v>-3.7</v>
       </c>
       <c r="R64" s="12">
-        <f t="shared" ref="R64:T64" si="60">R63</f>
+        <f t="shared" ref="R64:U64" si="87">R63</f>
         <v>-6.6</v>
       </c>
       <c r="S64" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="87"/>
         <v>-5.9</v>
       </c>
       <c r="T64" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="87"/>
         <v>-7.1</v>
       </c>
-      <c r="U64" s="14"/>
+      <c r="U64" s="12">
+        <f t="shared" si="87"/>
+        <v>-7</v>
+      </c>
       <c r="V64" s="12"/>
       <c r="W64" s="12"/>
       <c r="X64" s="12"/>
       <c r="Y64" s="12"/>
       <c r="Z64" s="12">
-        <f t="shared" ref="Z64:AF64" si="61">Z63</f>
+        <f t="shared" ref="Z64:AF64" si="88">Z63</f>
         <v>-1457.354</v>
       </c>
       <c r="AA64" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="88"/>
         <v>-7</v>
       </c>
       <c r="AB64" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="88"/>
         <v>-11</v>
       </c>
       <c r="AC64" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="88"/>
         <v>-7</v>
       </c>
       <c r="AD64" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="88"/>
         <v>17.7</v>
       </c>
       <c r="AE64" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="88"/>
         <v>-15.5</v>
       </c>
       <c r="AF64" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="88"/>
         <v>-4.2</v>
       </c>
       <c r="AG64" s="12">
         <f>AG63</f>
         <v>-23.5</v>
       </c>
-    </row>
-    <row r="65" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="14"/>
-      <c r="P65" s="14"/>
-      <c r="Q65" s="14"/>
-      <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
+      <c r="AH64" s="12">
+        <f>AH63</f>
+        <v>-25.7</v>
+      </c>
+      <c r="AI64" s="15"/>
+    </row>
+    <row r="65" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="4"/>
+      <c r="C65" s="2"/>
       <c r="T65" s="12"/>
-      <c r="U65" s="12"/>
       <c r="V65" s="12"/>
       <c r="W65" s="12"/>
       <c r="X65" s="12"/>
       <c r="Y65" s="12"/>
       <c r="Z65" s="12"/>
       <c r="AA65" s="12"/>
-      <c r="AB65" s="14"/>
-      <c r="AC65" s="14"/>
-      <c r="AD65" s="14"/>
-      <c r="AE65" s="14"/>
-      <c r="AF65" s="14"/>
-      <c r="AG65" s="14"/>
-    </row>
-    <row r="66" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AI65" s="15"/>
+    </row>
+    <row r="66" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="4"/>
       <c r="C66" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D66" s="14">
         <v>0</v>
@@ -7059,7 +8659,9 @@
       <c r="T66" s="14">
         <v>110</v>
       </c>
-      <c r="U66" s="12"/>
+      <c r="U66" s="14">
+        <v>140</v>
+      </c>
       <c r="V66" s="12"/>
       <c r="W66" s="12"/>
       <c r="X66" s="12"/>
@@ -7089,10 +8691,16 @@
       <c r="AG66" s="14">
         <v>180</v>
       </c>
-    </row>
-    <row r="67" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH66" s="14">
+        <v>840</v>
+      </c>
+      <c r="AI66" s="15"/>
+    </row>
+    <row r="67" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2"/>
+      <c r="B67" s="4"/>
       <c r="C67" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67" s="14">
         <v>-65</v>
@@ -7145,11 +8753,9 @@
       <c r="T67" s="14">
         <v>0</v>
       </c>
-      <c r="U67" s="12"/>
-      <c r="V67" s="14"/>
-      <c r="W67" s="14"/>
-      <c r="X67" s="14"/>
-      <c r="Y67" s="14"/>
+      <c r="U67" s="14">
+        <v>0</v>
+      </c>
       <c r="Z67" s="14">
         <v>-210</v>
       </c>
@@ -7174,10 +8780,16 @@
       <c r="AG67" s="14">
         <v>-210</v>
       </c>
-    </row>
-    <row r="68" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH67" s="14">
+        <v>-710</v>
+      </c>
+      <c r="AI67" s="15"/>
+    </row>
+    <row r="68" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2"/>
+      <c r="B68" s="4"/>
       <c r="C68" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D68" s="14">
         <v>-1.9</v>
@@ -7230,11 +8842,9 @@
       <c r="T68" s="14">
         <v>-3.2</v>
       </c>
-      <c r="U68" s="12"/>
-      <c r="V68" s="14"/>
-      <c r="W68" s="14"/>
-      <c r="X68" s="14"/>
-      <c r="Y68" s="14"/>
+      <c r="U68" s="14">
+        <v>-3.2</v>
+      </c>
       <c r="Z68" s="14">
         <v>0</v>
       </c>
@@ -7261,10 +8871,16 @@
       <c r="AG68" s="14">
         <v>-11.6</v>
       </c>
-    </row>
-    <row r="69" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH68" s="14">
+        <v>-12.5</v>
+      </c>
+      <c r="AI68" s="15"/>
+    </row>
+    <row r="69" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2"/>
+      <c r="B69" s="4"/>
       <c r="C69" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D69" s="14">
         <v>0</v>
@@ -7317,11 +8933,9 @@
       <c r="T69" s="14">
         <v>0</v>
       </c>
-      <c r="U69" s="12"/>
-      <c r="V69" s="14"/>
-      <c r="W69" s="14"/>
-      <c r="X69" s="14"/>
-      <c r="Y69" s="14"/>
+      <c r="U69" s="14">
+        <v>0</v>
+      </c>
       <c r="Z69" s="14">
         <v>0</v>
       </c>
@@ -7348,10 +8962,16 @@
       <c r="AG69" s="14">
         <v>50.9</v>
       </c>
-    </row>
-    <row r="70" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH69" s="14">
+        <v>31</v>
+      </c>
+      <c r="AI69" s="15"/>
+    </row>
+    <row r="70" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="4"/>
       <c r="C70" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D70" s="14">
         <v>0</v>
@@ -7404,11 +9024,9 @@
       <c r="T70" s="14">
         <v>0</v>
       </c>
-      <c r="U70" s="12"/>
-      <c r="V70" s="14"/>
-      <c r="W70" s="14"/>
-      <c r="X70" s="14"/>
-      <c r="Y70" s="14"/>
+      <c r="U70" s="14">
+        <v>0</v>
+      </c>
       <c r="Z70" s="14">
         <v>0</v>
       </c>
@@ -7433,10 +9051,16 @@
       <c r="AG70" s="14">
         <v>-0.7</v>
       </c>
-    </row>
-    <row r="71" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH70" s="14">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="AI70" s="15"/>
+    </row>
+    <row r="71" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="4"/>
       <c r="C71" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D71" s="14">
         <v>0</v>
@@ -7489,7 +9113,9 @@
       <c r="T71" s="14">
         <v>-155.1</v>
       </c>
-      <c r="U71" s="12"/>
+      <c r="U71" s="14">
+        <v>-147</v>
+      </c>
       <c r="V71" s="12"/>
       <c r="W71" s="12"/>
       <c r="X71" s="12"/>
@@ -7518,10 +9144,16 @@
       <c r="AG71" s="14">
         <v>-427.7</v>
       </c>
-    </row>
-    <row r="72" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH71" s="14">
+        <v>-566.6</v>
+      </c>
+      <c r="AI71" s="15"/>
+    </row>
+    <row r="72" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="4"/>
       <c r="C72" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="14">
         <v>0</v>
@@ -7574,11 +9206,9 @@
       <c r="T72" s="14">
         <v>0</v>
       </c>
-      <c r="U72" s="14"/>
-      <c r="V72" s="14"/>
-      <c r="W72" s="14"/>
-      <c r="X72" s="14"/>
-      <c r="Y72" s="14"/>
+      <c r="U72" s="14">
+        <v>-87.2</v>
+      </c>
       <c r="Z72" s="14">
         <v>0</v>
       </c>
@@ -7603,62 +9233,67 @@
       <c r="AG72" s="14">
         <v>-115.2</v>
       </c>
-      <c r="AI72" s="14"/>
-    </row>
-    <row r="73" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH72" s="14">
+        <v>-161.6</v>
+      </c>
+      <c r="AI72" s="15"/>
+    </row>
+    <row r="73" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="4"/>
       <c r="C73" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D73" s="12">
-        <f t="shared" ref="D73:P73" si="62">SUM(D66:D72)</f>
+        <f t="shared" ref="D73:P73" si="89">SUM(D66:D72)</f>
         <v>-66.900000000000006</v>
       </c>
       <c r="E73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-95.1</v>
       </c>
       <c r="F73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-122.4</v>
       </c>
       <c r="G73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-48.5</v>
       </c>
       <c r="H73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-79.3</v>
       </c>
       <c r="I73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-41.3</v>
       </c>
       <c r="J73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-121.8</v>
       </c>
       <c r="K73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-112.5</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-88.5</v>
       </c>
       <c r="M73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-175.70000000000002</v>
       </c>
       <c r="N73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-102.5</v>
       </c>
       <c r="O73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-167.60000000000002</v>
       </c>
       <c r="P73" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="89"/>
         <v>-152.4</v>
       </c>
       <c r="Q73" s="12">
@@ -7666,141 +9301,125 @@
         <v>-165.7</v>
       </c>
       <c r="R73" s="12">
-        <f t="shared" ref="R73:T73" si="63">SUM(R66:R72)</f>
+        <f t="shared" ref="R73:U73" si="90">SUM(R66:R72)</f>
         <v>-101.89999999999999</v>
       </c>
       <c r="S73" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="90"/>
         <v>-160.79999999999998</v>
       </c>
       <c r="T73" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="90"/>
         <v>-48.3</v>
       </c>
-      <c r="U73" s="14"/>
+      <c r="U73" s="12">
+        <f t="shared" si="90"/>
+        <v>-97.399999999999991</v>
+      </c>
       <c r="V73" s="12"/>
       <c r="W73" s="12"/>
       <c r="X73" s="12"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
-        <f t="shared" ref="Z73:AF73" si="64">SUM(Z66:Z72)</f>
+        <f t="shared" ref="Z73:AF73" si="91">SUM(Z66:Z72)</f>
         <v>1531.09</v>
       </c>
       <c r="AA73" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="91"/>
         <v>92.606999999999999</v>
       </c>
       <c r="AB73" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="91"/>
         <v>-218.82999999999998</v>
       </c>
       <c r="AC73" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="91"/>
         <v>-93.24</v>
       </c>
       <c r="AD73" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="91"/>
         <v>-405.3</v>
       </c>
       <c r="AE73" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="91"/>
         <v>-334.6</v>
       </c>
       <c r="AF73" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="91"/>
         <v>-354.9</v>
       </c>
       <c r="AG73" s="12">
         <f>SUM(AG66:AG72)</f>
         <v>-534.29999999999995</v>
       </c>
-    </row>
-    <row r="74" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="14"/>
-      <c r="O74" s="14"/>
-      <c r="P74" s="14"/>
-      <c r="Q74" s="14"/>
-      <c r="R74" s="14"/>
-      <c r="S74" s="14"/>
-      <c r="T74" s="14"/>
-      <c r="U74" s="14"/>
-      <c r="V74" s="14"/>
-      <c r="W74" s="14"/>
-      <c r="X74" s="14"/>
-      <c r="Y74" s="14"/>
-      <c r="Z74" s="14"/>
-      <c r="AA74" s="14"/>
-      <c r="AB74" s="14"/>
-      <c r="AC74" s="14"/>
-      <c r="AD74" s="14"/>
-      <c r="AE74" s="14"/>
-      <c r="AF74" s="14"/>
-      <c r="AG74" s="14"/>
-    </row>
-    <row r="75" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH73" s="12">
+        <f>SUM(AH66:AH72)</f>
+        <v>-580.80000000000007</v>
+      </c>
+      <c r="AI73" s="15"/>
+    </row>
+    <row r="74" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="2"/>
+      <c r="AI74" s="15"/>
+    </row>
+    <row r="75" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="4"/>
       <c r="C75" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D75" s="14">
-        <f t="shared" ref="D75:P75" si="65">D61+D64+D73</f>
+        <f t="shared" ref="D75:P75" si="92">D61+D64+D73</f>
         <v>2</v>
       </c>
       <c r="E75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>42.599999999999994</v>
       </c>
       <c r="F75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-14.000000000000028</v>
       </c>
       <c r="G75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-21.400000000000006</v>
       </c>
       <c r="H75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-20.700000000000003</v>
       </c>
       <c r="I75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>76.90000000000002</v>
       </c>
       <c r="J75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-0.29999999999999716</v>
       </c>
       <c r="K75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-52.90000000000002</v>
       </c>
       <c r="L75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-6.0000000000000142</v>
       </c>
       <c r="M75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>22.400000000000006</v>
       </c>
       <c r="N75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>26.500000000000028</v>
       </c>
       <c r="O75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-33.000000000000028</v>
       </c>
       <c r="P75" s="14">
-        <f t="shared" si="65"/>
+        <f t="shared" si="92"/>
         <v>-41.200000000000017</v>
       </c>
       <c r="Q75" s="14">
@@ -7808,141 +9427,121 @@
         <v>60.100000000000051</v>
       </c>
       <c r="R75" s="14">
-        <f t="shared" ref="R75:S75" si="66">R61+R64+R73</f>
+        <f t="shared" ref="R75:S75" si="93">R61+R64+R73</f>
         <v>134.19999999999999</v>
       </c>
       <c r="S75" s="14">
-        <f t="shared" si="66"/>
+        <f t="shared" si="93"/>
         <v>-92.09999999999998</v>
       </c>
       <c r="T75" s="14">
-        <f t="shared" ref="T75" si="67">T61+T64+T73</f>
+        <f t="shared" ref="T75:U75" si="94">T61+T64+T73</f>
         <v>10.099999999999987</v>
       </c>
-      <c r="U75" s="14"/>
-      <c r="V75" s="14"/>
-      <c r="W75" s="14"/>
-      <c r="X75" s="14"/>
-      <c r="Y75" s="14"/>
+      <c r="U75" s="14">
+        <f t="shared" si="94"/>
+        <v>59.3</v>
+      </c>
       <c r="Z75" s="14">
-        <f t="shared" ref="Z75:AG75" si="68">Z61+Z64+Z73</f>
+        <f t="shared" ref="Z75:AG75" si="95">Z61+Z64+Z73</f>
         <v>133.83599999999979</v>
       </c>
       <c r="AA75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>176.30700000000002</v>
       </c>
       <c r="AB75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>-90.63</v>
       </c>
       <c r="AC75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>27.124999999999972</v>
       </c>
       <c r="AD75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>-152.50000000000003</v>
       </c>
       <c r="AE75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>6.3999999999999773</v>
       </c>
       <c r="AF75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>36.800000000000068</v>
       </c>
       <c r="AG75" s="14">
-        <f t="shared" si="68"/>
+        <f t="shared" si="95"/>
         <v>8.9000000000000909</v>
       </c>
-    </row>
-    <row r="76" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="14"/>
-      <c r="P76" s="14"/>
-      <c r="Q76" s="14"/>
-      <c r="R76" s="14"/>
-      <c r="S76" s="14"/>
-      <c r="T76" s="14"/>
-      <c r="U76" s="14"/>
-      <c r="V76" s="14"/>
-      <c r="W76" s="14"/>
-      <c r="X76" s="14"/>
-      <c r="Y76" s="14"/>
-      <c r="Z76" s="14"/>
-      <c r="AA76" s="14"/>
-      <c r="AB76" s="14"/>
-      <c r="AC76" s="14"/>
-      <c r="AD76" s="14"/>
-      <c r="AE76" s="14"/>
-      <c r="AF76" s="14"/>
-      <c r="AG76" s="14"/>
-    </row>
-    <row r="77" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH75" s="14">
+        <f t="shared" ref="AH75" si="96">AH61+AH64+AH73</f>
+        <v>-9.3000000000000682</v>
+      </c>
+      <c r="AI75" s="15"/>
+    </row>
+    <row r="76" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="2"/>
+      <c r="AI76" s="15"/>
+    </row>
+    <row r="77" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="4"/>
       <c r="C77" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D77" s="14">
-        <f t="shared" ref="D77:P77" si="69">D61+D63</f>
+        <f t="shared" ref="D77:P77" si="97">D61+D63</f>
         <v>68.900000000000006</v>
       </c>
       <c r="E77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>137.69999999999999</v>
       </c>
       <c r="F77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>108.39999999999998</v>
       </c>
       <c r="G77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>27.099999999999994</v>
       </c>
       <c r="H77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>58.599999999999994</v>
       </c>
       <c r="I77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>118.20000000000002</v>
       </c>
       <c r="J77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>121.5</v>
       </c>
       <c r="K77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>59.59999999999998</v>
       </c>
       <c r="L77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>82.499999999999986</v>
       </c>
       <c r="M77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>198.10000000000002</v>
       </c>
       <c r="N77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>129.00000000000003</v>
       </c>
       <c r="O77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>134.6</v>
       </c>
       <c r="P77" s="14">
-        <f t="shared" si="69"/>
+        <f t="shared" si="97"/>
         <v>111.19999999999999</v>
       </c>
       <c r="Q77" s="14">
@@ -7950,56 +9549,60 @@
         <v>225.80000000000004</v>
       </c>
       <c r="R77" s="14">
-        <f t="shared" ref="R77:S77" si="70">R61+R63</f>
+        <f t="shared" ref="R77:S77" si="98">R61+R63</f>
         <v>236.1</v>
       </c>
       <c r="S77" s="14">
-        <f t="shared" si="70"/>
+        <f t="shared" si="98"/>
         <v>68.7</v>
       </c>
       <c r="T77" s="14">
-        <f t="shared" ref="T77" si="71">T61+T63</f>
+        <f t="shared" ref="T77:U77" si="99">T61+T63</f>
         <v>58.399999999999984</v>
       </c>
-      <c r="U77" s="14"/>
-      <c r="V77" s="14"/>
-      <c r="W77" s="14"/>
-      <c r="X77" s="14"/>
-      <c r="Y77" s="14"/>
+      <c r="U77" s="14">
+        <f t="shared" si="99"/>
+        <v>156.69999999999999</v>
+      </c>
       <c r="Z77" s="14">
-        <f t="shared" ref="Z77:AG77" si="72">Z61+Z63</f>
+        <f t="shared" ref="Z77:AG77" si="100">Z61+Z63</f>
         <v>-1397.2540000000001</v>
       </c>
       <c r="AA77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>83.7</v>
       </c>
       <c r="AB77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>128.19999999999999</v>
       </c>
       <c r="AC77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>120.36499999999997</v>
       </c>
       <c r="AD77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>252.79999999999998</v>
       </c>
       <c r="AE77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>341</v>
       </c>
       <c r="AF77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>391.70000000000005</v>
       </c>
       <c r="AG77" s="14">
-        <f t="shared" si="72"/>
+        <f t="shared" si="100"/>
         <v>543.20000000000005</v>
       </c>
-    </row>
-    <row r="79" spans="3:35" x14ac:dyDescent="0.25">
+      <c r="AH77" s="14">
+        <f t="shared" ref="AH77" si="101">AH61+AH63</f>
+        <v>571.5</v>
+      </c>
+      <c r="AI77" s="15"/>
+    </row>
+    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
@@ -8018,7 +9621,7 @@
       <c r="R79" s="11"/>
       <c r="S79" s="11"/>
     </row>
-    <row r="80" spans="3:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -9461,6 +11064,230 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAE7D72-8C86-3247-89D6-39A3266E6D81}">
+  <dimension ref="B5:N18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="38"/>
+    <col min="2" max="2" width="31.6640625" style="38" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="38" customWidth="1"/>
+    <col min="4" max="5" width="10.83203125" style="38"/>
+    <col min="6" max="6" width="14.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="10.83203125" style="38"/>
+    <col min="11" max="11" width="16.6640625" style="38" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="38"/>
+    <col min="13" max="13" width="15" style="38" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="38"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C5" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="N6" s="41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="40">
+        <v>116.6</v>
+      </c>
+      <c r="G7" s="40">
+        <v>126.6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="39">
+        <v>-0.21199999999999999</v>
+      </c>
+      <c r="G8" s="39">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="40">
+        <v>97.7</v>
+      </c>
+      <c r="G9" s="40">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="39">
+        <v>0.245</v>
+      </c>
+      <c r="G10" s="39">
+        <v>-0.29899999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="40">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="G11" s="40">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="39">
+        <v>2.4E-2</v>
+      </c>
+      <c r="G12" s="39">
+        <v>-4.7E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="40">
+        <v>9104</v>
+      </c>
+      <c r="G13" s="40">
+        <v>9244</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="39">
+        <v>0.108</v>
+      </c>
+      <c r="G14" s="39">
+        <v>0.13100000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" s="38">
+        <v>15.4</v>
+      </c>
+      <c r="G15" s="38">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="39">
+        <v>-0.113</v>
+      </c>
+      <c r="G16" s="39">
+        <v>-0.19700000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="38">
+        <v>11.1</v>
+      </c>
+      <c r="G17" s="38">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="39">
+        <v>-0.36399999999999999</v>
+      </c>
+      <c r="G18" s="39">
+        <v>-0.39400000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:N5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC8E745-DC06-8448-81B5-DC40131426CF}">
   <dimension ref="C4:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -9489,15 +11316,15 @@
       </c>
       <c r="D5" s="29">
         <f>Modell!$B$9/Modell!AI11</f>
-        <v>11.872365199808996</v>
+        <v>17.819735915197832</v>
       </c>
       <c r="E5" s="29">
         <f>Modell!$B$9/Modell!AJ11</f>
-        <v>11.307014476008568</v>
+        <v>16.971177062093172</v>
       </c>
       <c r="F5" s="29">
         <f>Modell!$B$9/Modell!AK11</f>
-        <v>10.768585215246256</v>
+        <v>16.163025773422071</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -9506,15 +11333,15 @@
       </c>
       <c r="D6" s="29">
         <f>Modell!$B$4/Modell!AI17</f>
-        <v>13.597035516832305</v>
+        <v>19.7924167539751</v>
       </c>
       <c r="E6" s="29">
         <f>Modell!$B$4/Modell!AJ17</f>
-        <v>12.949557635078385</v>
+        <v>18.849920718071527</v>
       </c>
       <c r="F6" s="35">
         <f>Modell!$B$4/Modell!AK17</f>
-        <v>12.332912033407988</v>
+        <v>17.952305445782407</v>
       </c>
     </row>
   </sheetData>
@@ -9522,7 +11349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3E88D3-8920-4B4C-A6FE-8E4196A56417}">
   <dimension ref="A3:GB23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -9600,7 +11427,7 @@
     </row>
     <row r="4" spans="1:184" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>51</v>
@@ -9742,7 +11569,7 @@
     <row r="6" spans="1:184" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <f>Y23</f>
-        <v>-0.15447078191300168</v>
+        <v>-5.0311385481994632E-2</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -11300,7 +13127,7 @@
       <c r="U18" s="9"/>
       <c r="V18" s="9"/>
       <c r="X18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y18" s="31">
         <v>0.08</v>
@@ -11384,7 +13211,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y19" s="31">
         <v>-0.01</v>
@@ -11392,7 +13219,7 @@
     </row>
     <row r="20" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25">
@@ -11468,7 +13295,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y20" s="32">
         <f>NPV(Y18,L15:GB15)</f>
@@ -11564,7 +13391,7 @@
     </row>
     <row r="22" spans="3:25" x14ac:dyDescent="0.25">
       <c r="X22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y22" s="17">
         <f>Y20/Y21</f>
@@ -11573,11 +13400,11 @@
     </row>
     <row r="23" spans="3:25" x14ac:dyDescent="0.25">
       <c r="X23" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y23" s="25">
         <f>(Y22-Modell!B4)/Modell!B4</f>
-        <v>-0.15447078191300168</v>
+        <v>-5.0311385481994632E-2</v>
       </c>
     </row>
   </sheetData>
